--- a/PA_communication_mapping_tables_20261021_1.xlsx
+++ b/PA_communication_mapping_tables_20261021_1.xlsx
@@ -15,12 +15,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Endo Schedule" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tax Invoice" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Collection Receipt" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Welcome Letter" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premium Details&gt;&gt;" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PC" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GCV" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCV" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2W" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deposit Slip-Cheque" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deposit Slip-Cash" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Welcome Letter" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premium Details&gt;&gt;" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PC" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GCV" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PCV" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2W" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Schedule-PCAR'!$A$1:$G$1</definedName>
@@ -2866,6 +2868,1751 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>Sr No</t>
+        </is>
+      </c>
+      <c r="B1" s="77" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
+          <t>Document Field (Cheque Deposit Slip)</t>
+        </is>
+      </c>
+      <c r="D1" s="77" t="inlineStr">
+        <is>
+          <t>PolicyDD / BCP Field</t>
+        </is>
+      </c>
+      <c r="E1" s="77" t="inlineStr">
+        <is>
+          <t>Associated API</t>
+        </is>
+      </c>
+      <c r="F1" s="77" t="inlineStr">
+        <is>
+          <t>Comments / Customer Clarification</t>
+        </is>
+      </c>
+      <c r="G1" s="77" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>Name of Account Holder</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="n"/>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>Fixed/configurable: "Protec Insurance".</t>
+        </is>
+      </c>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Account Type</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>Configurable, e.g. Current Account.</t>
+        </is>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Account Number</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Statement.AccountNo</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Statement carries AccountNo; full account number from bank master.</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Bank Name</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Configurable per deposit account.</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Branch Name</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Configurable per deposit account.</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>IFSC Code</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>Configurable per deposit account.</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Branch Code</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Statement.Office / Collection.BranchCode</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Mapping to Protec Branch code. Office on Statement (e.g. 500100).</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Pickup Address</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Branch address (India Branch module)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Branch master / India Branch module</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Combine &lt;address Line 1&gt;, &lt;address Line 2&gt;, &lt;City&gt;, &lt;District&gt;, &lt;State&gt;, &lt;PIN Code&gt;.</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Slip #</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Statement.StatementNo</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+GET /platform/bcp-core/... statement query (confirm endpoint)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Statement number is the deposit slip number.</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Date of Deposit</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Statement.Date</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>Statement date.</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Total Number of Instruments</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Count of Statement lines (Cheq/DD)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Count of instrument rows in the slip.</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Table</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Type</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Collection.PaymentMethod / Statement.InstrumentType</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
+CodeTable: BcpPaymentMethod</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Local Cheque / Outstation Cheque / Demand Draft. Local vs Outstation needs a flag; confirm source.</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Table</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Date</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Collection.InstrumentDate</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Template shows a date; same as Cheque Date? Confirm with Protec.</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Table</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Bank Name (drawee)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>Statement.BankName / Collection.BankName</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+GET /platform/bcp-core/collection/v1/getCollection</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Customer cheque bank.</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Table</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Branch Name (drawee)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>Statement.BranchName</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Customer cheque bank branch.</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Table</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>IFSC Code (drawee)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Statement.IFSCCode</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Customer cheque IFSC.</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Table</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Cheque No</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Statement.ChequeNo / Collection.InstrumentNo</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+GET /platform/bcp-core/collection/v1/getCollection</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Cheque / DD number.</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Table</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Cheque Date</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Statement.ChequeDate / Collection.InstrumentDate</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+GET /platform/bcp-core/collection/v1/getCollection</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>Cheque / DD date.</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Instrument Table</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>Statement.Amount / Collection.Amount</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>Per instrument.</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Total Amount</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>Sum of Amount</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Sum of instrument amounts (not shown in sample; add if needed).</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>Amount in Words</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>Derived from total</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Convert to words in template: Indian Rupees ... and Paisa ... ONLY.</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>Signature and Stamp - Protec General Insurance</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank; fixed wording "Protec General Insurance".</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>Date (Protec)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank.</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>Signature and Stamp - Bank Collection Agent</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank; fixed wording.</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>Date (Bank)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank.</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="78" t="inlineStr">
+        <is>
+          <t>Associated API reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="79" t="inlineStr">
+        <is>
+          <t>API purpose</t>
+        </is>
+      </c>
+      <c r="C30" s="79" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="D30" s="79" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="80" t="inlineStr">
+        <is>
+          <t>Statement (deposit slip header + lines)</t>
+        </is>
+      </c>
+      <c r="C31" s="80" t="inlineStr">
+        <is>
+          <t>BCP Statement page (bcp-core); Statement fields: StatementNo, Office, AccountNo, Date, Cash/Cheque, InstrumentType, Bank/Branch/IFSC, Cheque No/Date, Amount, denominations</t>
+        </is>
+      </c>
+      <c r="D31" s="80" t="inlineStr">
+        <is>
+          <t>Exact statement endpoint not in the BCP query skill; confirm with BCP team. URL via client.py get-url --page statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="80" t="inlineStr">
+        <is>
+          <t>Collection search</t>
+        </is>
+      </c>
+      <c r="C32" s="80" t="inlineStr">
+        <is>
+          <t>POST /platform/bcp-core/query/v1/queryEsData</t>
+        </is>
+      </c>
+      <c r="D32" s="80" t="inlineStr">
+        <is>
+          <t>Module=Collection; filter by ReceiptNo / CollectionNo / PolicyNo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="80" t="inlineStr">
+        <is>
+          <t>Collection by ID</t>
+        </is>
+      </c>
+      <c r="C33" s="80" t="inlineStr">
+        <is>
+          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
+        </is>
+      </c>
+      <c r="D33" s="80" t="inlineStr">
+        <is>
+          <t>ID must be signed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="80" t="inlineStr">
+        <is>
+          <t>Offset / Statement offset</t>
+        </is>
+      </c>
+      <c r="C34" s="80" t="inlineStr">
+        <is>
+          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Offset)</t>
+        </is>
+      </c>
+      <c r="D34" s="80" t="inlineStr">
+        <is>
+          <t>Offset record has StatementNo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="80" t="inlineStr">
+        <is>
+          <t>Code tables</t>
+        </is>
+      </c>
+      <c r="C35" s="80" t="inlineStr">
+        <is>
+          <t>BcpPaymentMethod, BcpCollectionType</t>
+        </is>
+      </c>
+      <c r="D35" s="80" t="inlineStr">
+        <is>
+          <t>Instrument type descriptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="80" t="inlineStr">
+        <is>
+          <t>Document generation</t>
+        </is>
+      </c>
+      <c r="C36" s="80" t="inlineStr">
+        <is>
+          <t>InsureMO Output Service: template upload + print task (PDF)</t>
+        </is>
+      </c>
+      <c r="D36" s="80" t="inlineStr">
+        <is>
+          <t>Handlebars template from the Excel slip.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="77" t="inlineStr">
+        <is>
+          <t>Sr No</t>
+        </is>
+      </c>
+      <c r="B1" s="77" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C1" s="77" t="inlineStr">
+        <is>
+          <t>Document Field (Cash Deposit Slip)</t>
+        </is>
+      </c>
+      <c r="D1" s="77" t="inlineStr">
+        <is>
+          <t>PolicyDD / BCP Field</t>
+        </is>
+      </c>
+      <c r="E1" s="77" t="inlineStr">
+        <is>
+          <t>Associated API</t>
+        </is>
+      </c>
+      <c r="F1" s="77" t="inlineStr">
+        <is>
+          <t>Comments / Customer Clarification</t>
+        </is>
+      </c>
+      <c r="G1" s="77" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>Name of Account Holder</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="n"/>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F2" s="23" t="inlineStr">
+        <is>
+          <t>Fixed/configurable: "Protec Insurance".</t>
+        </is>
+      </c>
+      <c r="G2" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Account Type</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="n"/>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
+          <t>Configurable, e.g. Current Account.</t>
+        </is>
+      </c>
+      <c r="G3" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>Account Number</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>Statement.AccountNo</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>Statement carries AccountNo; full account number from bank master.</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Bank Name</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t>Configurable per deposit account.</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>Branch Name</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>Configurable per deposit account.</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Bank Account (Header)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>IFSC Code</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Company bank account master (Protec) - configurable</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>Configurable per deposit account.</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>Branch Code</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>Statement.Office / Collection.BranchCode</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>Mapping to Protec Branch code. Office on Statement (e.g. 500100).</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Pickup Address</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Branch address (India Branch module)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>Branch master / India Branch module</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>Combine &lt;address Line 1&gt;, &lt;address Line 2&gt;, &lt;City&gt;, &lt;District&gt;, &lt;State&gt;, &lt;PIN Code&gt;.</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Slip #</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>Statement.StatementNo</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"
+GET /platform/bcp-core/... statement query (confirm endpoint)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>Statement number is the deposit slip number.</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Deposit Info (Header)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Date of Deposit</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Statement.Date</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>Statement date.</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>Denomination Table</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>Notes / Coins (fixed)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>Fixed lines: Notes 500,100,50,20,10; Coins 20,10,5,2,1.</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Denomination Table</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Denomination</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Statement columns 500/100/50/20/10/1</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>Statement carries denomination columns (Notes 500..10, Coins 1). Coins 20/10/5/2 not in Statement; confirm.</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>Denomination Table</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>Pieces</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>Statement.&lt;denomination&gt; count</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>BCP Statement (bcp-core) - page "statement"</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>Piece count per denomination.</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Denomination Table</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>Denomination x Pieces</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>Calculated in template.</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Denomination Table</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank / free text.</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Sum of Amount</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>Sum of denomination amounts; must equal Collection.Amount for the statement.</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>Amount in Words</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>Derived from total</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>Convert to words in template: Indian Rupees ... and Paisa ... ONLY.</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Signature and Stamp - Protec General Insurance</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank; fixed wording.</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>Date (Protec)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank.</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Signature and Stamp - Bank Collection Agent</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank; fixed wording.</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>Signature</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>Date (Bank)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>Keep blank.</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="78" t="inlineStr">
+        <is>
+          <t>Associated API reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="79" t="inlineStr">
+        <is>
+          <t>API purpose</t>
+        </is>
+      </c>
+      <c r="C26" s="79" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="D26" s="79" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="80" t="inlineStr">
+        <is>
+          <t>Statement (deposit slip header + lines)</t>
+        </is>
+      </c>
+      <c r="C27" s="80" t="inlineStr">
+        <is>
+          <t>BCP Statement page (bcp-core); Statement fields: StatementNo, Office, AccountNo, Date, Cash/Cheque, InstrumentType, Bank/Branch/IFSC, Cheque No/Date, Amount, denominations</t>
+        </is>
+      </c>
+      <c r="D27" s="80" t="inlineStr">
+        <is>
+          <t>Exact statement endpoint not in the BCP query skill; confirm with BCP team. URL via client.py get-url --page statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="80" t="inlineStr">
+        <is>
+          <t>Collection search</t>
+        </is>
+      </c>
+      <c r="C28" s="80" t="inlineStr">
+        <is>
+          <t>POST /platform/bcp-core/query/v1/queryEsData</t>
+        </is>
+      </c>
+      <c r="D28" s="80" t="inlineStr">
+        <is>
+          <t>Module=Collection; filter by ReceiptNo / CollectionNo / PolicyNo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="80" t="inlineStr">
+        <is>
+          <t>Collection by ID</t>
+        </is>
+      </c>
+      <c r="C29" s="80" t="inlineStr">
+        <is>
+          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
+        </is>
+      </c>
+      <c r="D29" s="80" t="inlineStr">
+        <is>
+          <t>ID must be signed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="80" t="inlineStr">
+        <is>
+          <t>Offset / Statement offset</t>
+        </is>
+      </c>
+      <c r="C30" s="80" t="inlineStr">
+        <is>
+          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Offset)</t>
+        </is>
+      </c>
+      <c r="D30" s="80" t="inlineStr">
+        <is>
+          <t>Offset record has StatementNo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="80" t="inlineStr">
+        <is>
+          <t>Code tables</t>
+        </is>
+      </c>
+      <c r="C31" s="80" t="inlineStr">
+        <is>
+          <t>BcpPaymentMethod, BcpCollectionType</t>
+        </is>
+      </c>
+      <c r="D31" s="80" t="inlineStr">
+        <is>
+          <t>Instrument type descriptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="80" t="inlineStr">
+        <is>
+          <t>Document generation</t>
+        </is>
+      </c>
+      <c r="C32" s="80" t="inlineStr">
+        <is>
+          <t>InsureMO Output Service: template upload + print task (PDF)</t>
+        </is>
+      </c>
+      <c r="D32" s="80" t="inlineStr">
+        <is>
+          <t>Handlebars template from the Excel slip.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="FFFF0000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2885,7 +4632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2898,7 +4645,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -3657,7 +5404,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -4634,7 +6381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -5408,7 +7155,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>

--- a/PA_communication_mapping_tables_20261021_1.xlsx
+++ b/PA_communication_mapping_tables_20261021_1.xlsx
@@ -17282,7 +17282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -17342,14 +17342,14 @@
       </c>
       <c r="C2" s="23" t="inlineStr">
         <is>
-          <t>Company Logo</t>
+          <t>Company Name / Logo</t>
         </is>
       </c>
       <c r="D2" s="23" t="n"/>
       <c r="E2" s="23" t="n"/>
       <c r="F2" s="23" t="inlineStr">
         <is>
-          <t>Need configurable</t>
+          <t>Need configurable ("Protec General Insurance").</t>
         </is>
       </c>
       <c r="G2" s="23" t="inlineStr">
@@ -17369,14 +17369,18 @@
       </c>
       <c r="C3" s="23" t="inlineStr">
         <is>
-          <t>Company Name</t>
-        </is>
-      </c>
-      <c r="D3" s="23" t="n"/>
+          <t>QR Code - scan to verify</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>Verification URL + Collection.ReceiptNo</t>
+        </is>
+      </c>
       <c r="E3" s="23" t="n"/>
       <c r="F3" s="23" t="inlineStr">
         <is>
-          <t>Need configurable</t>
+          <t>Generated at print time. Needs receipt verification page (www.XXXX.com/verify-receipt) from Protec.</t>
         </is>
       </c>
       <c r="G3" s="23" t="inlineStr">
@@ -17423,12 +17427,12 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>Customer Code</t>
+          <t>Receipt No</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>Collection.PayerPayeeCode</t>
+          <t>Collection.ReceiptNo / CollectionNo</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
@@ -17439,7 +17443,7 @@
       </c>
       <c r="F5" s="23" t="inlineStr">
         <is>
-          <t>Payer / policyholder customer code.</t>
+          <t>Receipt number generated by BCP.</t>
         </is>
       </c>
       <c r="G5" s="23" t="n"/>
@@ -17455,12 +17459,12 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Customer Name</t>
+          <t>Collection Date</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>Collection.PayerPayeeName</t>
+          <t>Collection.ReceiptDate</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -17471,7 +17475,7 @@
       </c>
       <c r="F6" s="23" t="inlineStr">
         <is>
-          <t>Payer name.</t>
+          <t>ReceiptDate agreed (many date-time fields in BCP).</t>
         </is>
       </c>
       <c r="G6" s="23" t="n"/>
@@ -17487,31 +17491,30 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>Customer Address</t>
+          <t>Payer Type</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>Policy.PolicyCustomer[0].AddressLine1
-Policy.PolicyCustomer[0].AddressLine2
-Policy.PolicyCustomer[0].AddressLine3
-Policy.PolicyCustomer[0].IN_City
-Policy.PolicyCustomer[0].IN_District
-Policy.PolicyCustomer[0].IN_State
-Policy.PolicyCustomer[0].IN_PinCode</t>
+          <t>Collection.PayerPayeeType (confirm field)</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>Policy/Proposal load: insuremo-gi-pa-query (policy by proposalNo / policyNo)</t>
+          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
+GET /platform/bcp-core/collection/v1/getCollection</t>
         </is>
       </c>
       <c r="F7" s="23" t="inlineStr">
         <is>
-          <t>Combine &lt;address Line 1&gt;, &lt;address Line 2&gt;, &lt;Address Line 3&gt; &lt;City&gt;, &lt;District&gt;, &lt;State&gt;, &lt;PIN Code&gt;. Not stored on Collection; take from proposal.</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="n"/>
+          <t>Customer / Agent / Intermediary etc. Confirm field and code table.</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="n">
@@ -17524,23 +17527,24 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Collection No</t>
+          <t>Office / Branch Code</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>Collection.CollectionNo</t>
+          <t>Collection.BranchCode / Policy.OrgCode</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
           <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
-GET /platform/bcp-core/collection/v1/getCollection</t>
+GET /platform/bcp-core/collection/v1/getCollection
+Branch master / India Branch module</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>Receipt reference generated by BCP.</t>
+          <t>Mapping to Protec Branch code.</t>
         </is>
       </c>
       <c r="G8" s="23" t="n"/>
@@ -17556,12 +17560,12 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Collection Date</t>
+          <t>Payer Code</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Collection.ConfirmTime</t>
+          <t>Collection.PayerPayeeCode</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -17572,14 +17576,10 @@
       </c>
       <c r="F9" s="23" t="inlineStr">
         <is>
-          <t>Date collection confirmed. Confirm with Protec whether to use ConfirmTime or creation time.</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>Pending Protec confirmation</t>
-        </is>
-      </c>
+          <t>Covers customers and agents/intermediaries.</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="n">
@@ -17592,23 +17592,23 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Amount Collected</t>
+          <t>Intermediary Code</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Collection.Amount</t>
+          <t>Collection.ChannelCode / Policy.PolicyAgent[IsLeader=Y].AgentCode</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
           <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
-GET /platform/bcp-core/collection/v1/getCollection</t>
+Policy load (gi-pa-query)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t>Total collected amount, INR.</t>
+          <t>Main Agent Code (IsLeader = Y). Blank for direct business.</t>
         </is>
       </c>
       <c r="G10" s="23" t="n"/>
@@ -17624,18 +17624,23 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>Amount in Words</t>
+          <t>Payer Name</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
-          <t>Derived from Collection.Amount</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n"/>
+          <t>Collection.PayerPayeeName</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
+GET /platform/bcp-core/collection/v1/getCollection</t>
+        </is>
+      </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>Convert amount to words in output template (INR, Rupees ... Only).</t>
+          <t>Covers customers and agents/intermediaries.</t>
         </is>
       </c>
       <c r="G11" s="23" t="n"/>
@@ -17651,12 +17656,12 @@
       </c>
       <c r="C12" s="23" t="inlineStr">
         <is>
-          <t>Office/ Branch Code</t>
+          <t>Amount Collected (Rs.)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
         <is>
-          <t>Collection.BranchCode / Policy.OrgCode</t>
+          <t>Collection.Amount</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -17667,7 +17672,7 @@
       </c>
       <c r="F12" s="23" t="inlineStr">
         <is>
-          <t>Mapping to Protec Branch code/name (same as Policy Issuing Office in Schedule).</t>
+          <t>Total collected, INR, Indian digit grouping (1,00,000.00).</t>
         </is>
       </c>
       <c r="G12" s="23" t="n"/>
@@ -17678,23 +17683,23 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Receipt Details</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>Sr. No</t>
+          <t>Amount in Words</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Derived from Collection.Amount</t>
         </is>
       </c>
       <c r="E13" s="23" t="n"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
-          <t>Line sequence, one row per CollectionDetail.</t>
+          <t>Convert to words in output template.</t>
         </is>
       </c>
       <c r="G13" s="23" t="n"/>
@@ -17705,28 +17710,23 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
         <is>
-          <t>Proposal Ref. No</t>
+          <t>Sr. No</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>Policy.ProposalNo / Collection.ReferenceNo</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
-        <is>
-          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Arap, ProposalNo)
-POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="n"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
-          <t>Proposal number the deposit is held against (suspense until policy issuance).</t>
+          <t>One row per CollectionDetail.</t>
         </is>
       </c>
       <c r="G14" s="23" t="n"/>
@@ -17737,31 +17737,35 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
         <is>
-          <t>Intermediary Code</t>
+          <t>Collection Type</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
         <is>
-          <t>Collection.ChannelCode / Policy.PolicyAgent[IsLeader=Y].AgentCode</t>
+          <t>Collection.CollectionType / BizTransType</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
         <is>
           <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
-Policy load (gi-pa-query)</t>
+CodeTable: BcpCollectionType, BizTransactionType</t>
         </is>
       </c>
       <c r="F15" s="23" t="inlineStr">
         <is>
-          <t>Main Agent Code (IsLeader = Y).</t>
-        </is>
-      </c>
-      <c r="G15" s="23" t="n"/>
+          <t>Premium - New Business / Renewal, Endorsement Premium, Claim Recovery - Salvage / Subrogation. Confirm each type is derivable from CollectionType + BizTransType.</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="23" t="n">
@@ -17769,27 +17773,28 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
         <is>
-          <t>Amount Collected (Rs.)</t>
+          <t>Product / LoB</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>CollectionDetail.Amount</t>
+          <t>BizTransaction.ProductCode</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
         <is>
-          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
+          <t>GET /platform/bcp-core/bizTransaction/v1/loadBizTransaction
+CodeTable: Products</t>
         </is>
       </c>
       <c r="F16" s="23" t="inlineStr">
         <is>
-          <t>Detail-level amount, sums to header Amount Collected.</t>
+          <t>Show product / line of business name, not code.</t>
         </is>
       </c>
       <c r="G16" s="23" t="n"/>
@@ -17800,28 +17805,29 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
         <is>
-          <t>Mode of Payment</t>
+          <t>Reference No</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Collection.PaymentMethod</t>
+          <t>Proposal / Policy / Endorsement / Claim No</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
           <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
-CodeTable: BcpPaymentMethod</t>
+GET /platform/bcp-core/bizTransaction/v1/loadBizTransaction
+POST queryEsData (Module=Arap, PolicyNo / ProposalNo / ClaimNo)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
         <is>
-          <t>Show code table description (Cash/Cheque/DD/etc.).</t>
+          <t>PQ- proposal/quote, POL- policy, END- endorsement, CLM- claim. Source number depends on Collection Type.</t>
         </is>
       </c>
       <c r="G17" s="23" t="n"/>
@@ -17832,35 +17838,30 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
         <is>
-          <t>Bank Name</t>
+          <t>Amount (Rs.)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Collection.BankName / BankCode</t>
+          <t>CollectionDetail.Amount</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
         <is>
-          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
-GET /platform/bcp-core/collection/v1/getCollection</t>
+          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
         <is>
-          <t>Show only for non-cash modes. Confirm field name with BCP config.</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="inlineStr">
-        <is>
-          <t>Pending confirmation</t>
-        </is>
-      </c>
+          <t>Detail-level amount; lines sum to Amount Collected.</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="23" t="n">
@@ -17868,34 +17869,31 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
         <is>
-          <t>CHQ/CC/DD No</t>
+          <t>Mode of Payment</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
         <is>
-          <t>Collection.InstrumentNo / ChequeNo</t>
+          <t>Collection.PaymentMethod</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
         <is>
-          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
+          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
+CodeTable: BcpPaymentMethod</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>Show only for Cheque/DD/Card. Confirm field name.</t>
-        </is>
-      </c>
-      <c r="G19" s="23" t="inlineStr">
-        <is>
-          <t>Pending confirmation</t>
-        </is>
-      </c>
+          <t>Cheque, NEFT, RTGS, UPI etc. Confirm all modes exist in BcpPaymentMethod.</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="23" t="n">
@@ -17903,27 +17901,28 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
         <is>
-          <t>CHQ/DD/BC Dt.</t>
+          <t>Bank Name / Branch / IFSC</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
         <is>
-          <t>Collection.InstrumentDate / ChequeDate</t>
+          <t>Collection.BankName, BankCode, IFSCCode (confirm fields)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
         <is>
-          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
+          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Collection)
+GET /platform/bcp-core/collection/v1/getCollection</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
         <is>
-          <t>Instrument date. Confirm field name.</t>
+          <t>Customer bank on instrument/payment. Blank for cash.</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -17938,17 +17937,17 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Collection Detail Table</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Instrument / UTR / Txn Ref No</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t>Collection.Remark</t>
+          <t>Collection.InstrumentNo / UTR / TransactionRefNo (confirm field)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -17958,10 +17957,14 @@
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
-          <t>Free text.</t>
-        </is>
-      </c>
-      <c r="G21" s="23" t="n"/>
+          <t>Cheque/DD number, or UTR/transaction reference for NEFT/RTGS/UPI.</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="n">
@@ -17969,26 +17972,34 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Collection Table</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
         <is>
-          <t>This is a system-generated receipt and does not require a signature</t>
+          <t>Instrument Date</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="23" t="n"/>
+          <t>Collection.InstrumentDate (confirm field)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
+        </is>
+      </c>
       <c r="F22" s="23" t="inlineStr">
         <is>
-          <t>Fixed wording.</t>
-        </is>
-      </c>
-      <c r="G22" s="23" t="n"/>
+          <t>Cheque/DD date or transaction date.</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>Pending confirmation</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="n">
@@ -18001,7 +18012,7 @@
       </c>
       <c r="C23" s="23" t="inlineStr">
         <is>
-          <t>Note: receipt is issued as acknowledgement of deposit ... refunded in full</t>
+          <t>This is a system-generated receipt and does not require a signature</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -18012,7 +18023,7 @@
       <c r="E23" s="23" t="n"/>
       <c r="F23" s="23" t="inlineStr">
         <is>
-          <t>Fixed wording (long disclaimer paragraph in template).</t>
+          <t>Fixed wording.</t>
         </is>
       </c>
       <c r="G23" s="23" t="n"/>
@@ -18028,21 +18039,21 @@
       </c>
       <c r="C24" s="23" t="inlineStr">
         <is>
-          <t>Registered Office (Address)</t>
-        </is>
-      </c>
-      <c r="D24" s="23" t="n"/>
+          <t>Note: acknowledgement of deposit ... refunded in full</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="E24" s="23" t="n"/>
       <c r="F24" s="23" t="inlineStr">
         <is>
-          <t>Need configurable.</t>
-        </is>
-      </c>
-      <c r="G24" s="23" t="inlineStr">
-        <is>
-          <t>Pending Protec provide before go-live</t>
-        </is>
-      </c>
+          <t>Fixed wording (updated to include electronic payment).</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="23" t="n">
@@ -18055,7 +18066,7 @@
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>IRDAI Regn. No.</t>
+          <t>Company Name / Registered Office</t>
         </is>
       </c>
       <c r="D25" s="23" t="n"/>
@@ -18082,21 +18093,25 @@
       </c>
       <c r="C26" s="23" t="inlineStr">
         <is>
-          <t>GSTIN</t>
+          <t>CIN / IRDAI Regn. No. / GSTIN</t>
         </is>
       </c>
       <c r="D26" s="23" t="n"/>
       <c r="E26" s="23" t="inlineStr">
         <is>
-          <t>Branch GSTIN: India Branch module</t>
+          <t>Branch master / India Branch module</t>
         </is>
       </c>
       <c r="F26" s="23" t="inlineStr">
         <is>
-          <t>Organization on policy; branch has its GSTIN in India Branch module (as Tax Invoice).</t>
-        </is>
-      </c>
-      <c r="G26" s="23" t="n"/>
+          <t>CIN and IRDAI No need configurable. GSTIN from India Branch module (as Tax Invoice).</t>
+        </is>
+      </c>
+      <c r="G26" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="n">
@@ -18116,7 +18131,7 @@
       <c r="E27" s="23" t="n"/>
       <c r="F27" s="23" t="inlineStr">
         <is>
-          <t>All need configurable.</t>
+          <t>Need configurable.</t>
         </is>
       </c>
       <c r="G27" s="23" t="inlineStr">
@@ -18125,163 +18140,257 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>Grievances: Grievance Officer</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="inlineStr">
+        <is>
+          <t>Need configurable (email / phone).</t>
+        </is>
+      </c>
+      <c r="G28" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>IRDAI Bima Bharosa</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="inlineStr">
+        <is>
+          <t>Fixed wording: bimabharosa.irdai.gov.in.</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="n"/>
+    </row>
     <row r="30">
-      <c r="B30" s="78" t="inlineStr">
+      <c r="A30" s="23" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="C30" s="23" t="inlineStr">
+        <is>
+          <t>Verify this receipt: QR code or website</t>
+        </is>
+      </c>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="inlineStr">
+        <is>
+          <t>Fixed wording; website needs configurable.</t>
+        </is>
+      </c>
+      <c r="G30" s="23" t="inlineStr">
+        <is>
+          <t>Pending Protec provide before go-live</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="78" t="inlineStr">
         <is>
           <t>Associated API reference</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="79" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="79" t="inlineStr">
         <is>
           <t>API purpose</t>
         </is>
       </c>
-      <c r="C31" s="79" t="inlineStr">
+      <c r="C34" s="79" t="inlineStr">
         <is>
           <t>Endpoint</t>
         </is>
       </c>
-      <c r="D31" s="79" t="inlineStr">
+      <c r="D34" s="79" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="80" t="inlineStr">
-        <is>
-          <t>Collection search (list/query)</t>
-        </is>
-      </c>
-      <c r="C32" s="80" t="inlineStr">
-        <is>
-          <t>POST /platform/bcp-core/query/v1/queryEsData</t>
-        </is>
-      </c>
-      <c r="D32" s="80" t="inlineStr">
-        <is>
-          <t>Body: {"Module":"Collection","FuzzyConditions":{"ReceiptNo"|"CollectionNo"|"PolicyNo": ...},"PageNo":1,"PageSize":1000}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="80" t="inlineStr">
-        <is>
-          <t>Collection by ID</t>
-        </is>
-      </c>
-      <c r="C33" s="80" t="inlineStr">
-        <is>
-          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
-        </is>
-      </c>
-      <c r="D33" s="80" t="inlineStr">
-        <is>
-          <t>Collection ID must be signed (numeric,hash); returns header + CollectionDetail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="80" t="inlineStr">
-        <is>
-          <t>BizTransaction (collection)</t>
-        </is>
-      </c>
-      <c r="C34" s="80" t="inlineStr">
-        <is>
-          <t>GET /platform/bcp-core/bizTransaction/v1/loadBizTransaction</t>
-        </is>
-      </c>
-      <c r="D34" s="80" t="inlineStr">
-        <is>
-          <t>Optional: fee/channel/payment method at transaction level.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="80" t="inlineStr">
         <is>
-          <t>Suspense (deposit held)</t>
+          <t>Collection search</t>
         </is>
       </c>
       <c r="C35" s="80" t="inlineStr">
         <is>
-          <t>GET /platform/bcp-core/suspense/v1/loadSuspenseById</t>
+          <t>POST /platform/bcp-core/query/v1/queryEsData</t>
         </is>
       </c>
       <c r="D35" s="80" t="inlineStr">
         <is>
-          <t>CollectionDetail.RefId links to Suspense (RefType=2).</t>
+          <t>Module=Collection; filter by ReceiptNo / CollectionNo / PolicyNo.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="80" t="inlineStr">
         <is>
-          <t>Create / confirm collection (source of data)</t>
+          <t>Collection by ID</t>
         </is>
       </c>
       <c r="C36" s="80" t="inlineStr">
         <is>
-          <t>collectionApplication, confirmCollection, policyCollectionAndOffset, producerCollect</t>
+          <t>GET /platform/bcp-core/collection/v1/getCollection</t>
         </is>
       </c>
       <c r="D36" s="80" t="inlineStr">
         <is>
-          <t>Write-side BCP APIs that create the record the receipt prints.</t>
+          <t>ID must be signed (numeric,hash). Returns header + CollectionDetail.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="80" t="inlineStr">
         <is>
-          <t>Policy / proposal (address, agent, org)</t>
+          <t>BizTransaction</t>
         </is>
       </c>
       <c r="C37" s="80" t="inlineStr">
         <is>
-          <t>insuremo-gi-pa-query: load policy by proposalNo / policyNo</t>
+          <t>GET /platform/bcp-core/bizTransaction/v1/loadBizTransaction</t>
         </is>
       </c>
       <c r="D37" s="80" t="inlineStr">
         <is>
-          <t>For customer address, intermediary, branch.</t>
+          <t>Product, transaction type, channel.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="80" t="inlineStr">
         <is>
-          <t>Code tables</t>
+          <t>ARAP search (reference no)</t>
         </is>
       </c>
       <c r="C38" s="80" t="inlineStr">
         <is>
-          <t>CodeTable: BcpPaymentMethod, BcpCollectionType, BcpCollectionStatus</t>
+          <t>POST /platform/bcp-core/query/v1/queryEsData (Module=Arap)</t>
         </is>
       </c>
       <c r="D38" s="80" t="inlineStr">
         <is>
-          <t>Translate codes to descriptions.</t>
+          <t>By PolicyNo / ProposalNo / ClaimNo.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="80" t="inlineStr">
         <is>
+          <t>Suspense</t>
+        </is>
+      </c>
+      <c r="C39" s="80" t="inlineStr">
+        <is>
+          <t>GET /platform/bcp-core/suspense/v1/loadSuspenseById</t>
+        </is>
+      </c>
+      <c r="D39" s="80" t="inlineStr">
+        <is>
+          <t>CollectionDetail.RefId links to Suspense (RefType=2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="80" t="inlineStr">
+        <is>
+          <t>Create / confirm collection</t>
+        </is>
+      </c>
+      <c r="C40" s="80" t="inlineStr">
+        <is>
+          <t>collectionApplication, confirmCollection, policyCollectionAndOffset, producerCollect</t>
+        </is>
+      </c>
+      <c r="D40" s="80" t="inlineStr">
+        <is>
+          <t>Write-side APIs that create the record the receipt prints.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="80" t="inlineStr">
+        <is>
+          <t>Policy / proposal</t>
+        </is>
+      </c>
+      <c r="C41" s="80" t="inlineStr">
+        <is>
+          <t>insuremo-gi-pa-query: load by proposalNo / policyNo</t>
+        </is>
+      </c>
+      <c r="D41" s="80" t="inlineStr">
+        <is>
+          <t>Intermediary and branch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="80" t="inlineStr">
+        <is>
+          <t>Code tables</t>
+        </is>
+      </c>
+      <c r="C42" s="80" t="inlineStr">
+        <is>
+          <t>BcpPaymentMethod, BcpCollectionType, BizTransactionType, Products</t>
+        </is>
+      </c>
+      <c r="D42" s="80" t="inlineStr">
+        <is>
+          <t>Translate codes to descriptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="80" t="inlineStr">
+        <is>
           <t>Document generation</t>
         </is>
       </c>
-      <c r="C39" s="80" t="inlineStr">
+      <c r="C43" s="80" t="inlineStr">
         <is>
           <t>InsureMO Output Service: template upload + print task (PDF)</t>
         </is>
       </c>
-      <c r="D39" s="80" t="inlineStr">
-        <is>
-          <t>Handlebars template built from the Word receipt.</t>
+      <c r="D43" s="80" t="inlineStr">
+        <is>
+          <t>Handlebars template from GI_Collection_Receipt_Template_v5.docx.</t>
         </is>
       </c>
     </row>

--- a/PA_communication_mapping_tables_20261021_1.xlsx
+++ b/PA_communication_mapping_tables_20261021_1.xlsx
@@ -19,13 +19,15 @@
     <sheet name="Collection Receipt-Mapping" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="Collection Receipt-Example" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="Deposit Slip-Cheque" sheetId="11" state="visible" r:id="rId13"/>
-    <sheet name="Deposit Slip-Cash" sheetId="12" state="visible" r:id="rId14"/>
-    <sheet name="Welcome Letter" sheetId="13" state="visible" r:id="rId15"/>
-    <sheet name="Premium Details&gt;&gt;" sheetId="14" state="visible" r:id="rId16"/>
-    <sheet name="PC" sheetId="15" state="visible" r:id="rId17"/>
-    <sheet name="GCV" sheetId="16" state="visible" r:id="rId18"/>
-    <sheet name="PCV" sheetId="17" state="visible" r:id="rId19"/>
-    <sheet name="2W" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="Deposit Slip-Cheque Example" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Deposit Slip-Cash" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="Deposit Slip-Cash Example" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Welcome Letter" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Premium Details&gt;&gt;" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="PC" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="GCV" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="PCV" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="2W" sheetId="20" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Schedule-PCAR'!$A$1:$G$1</definedName>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2594" uniqueCount="1097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="1141">
   <si>
     <t xml:space="preserve">Sr No</t>
   </si>
@@ -2896,6 +2898,126 @@
     <t xml:space="preserve">Handlebars template from the Excel slip.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cheque Deposit Slip - Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account details, instrument types and Statement values are from DepositSlipSample.xlsx. Bank, cheque number and amount values are illustrative (blank in the sample).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protec Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current Account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andheri (East) branch (from India Branch module)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00012345678900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICICI Bank Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andheri (East)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICICI00001234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local Cheque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andheri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">000101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outstation Cheque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">000202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demand Draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chennai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTIB0000016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DD3003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bandra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICIC0000014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">000404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dadar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARB0DADXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">000505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kotak Mahindra Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KKBK0000650</t>
+  </si>
+  <si>
+    <t xml:space="preserve">000606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canara Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juhu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNRB0000890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">000707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punjab National Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vile Parle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PUNB0123400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">000808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian Rupees Two Lakh Seventeen Thousand Five Hundred and Paisa Zero ONLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature and Stamp - Protec General Insurance / Date: ____</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signature and Stamp - Bank Collection Agent / Date: ____</t>
+  </si>
+  <si>
     <t xml:space="preserve">Document Field (Cash Deposit Slip)</t>
   </si>
   <si>
@@ -2939,6 +3061,18 @@
   </si>
   <si>
     <t xml:space="preserve">Sum of denomination amounts; must equal Collection.Amount for the statement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash Deposit Slip - Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All values (account details, denominations, pieces, Statement 1001) are from DepositSlipSample.xlsx.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian Rupees Nineteen Thousand Three Hundred Thirty and Paisa Zero ONLY</t>
   </si>
   <si>
     <t xml:space="preserve">Pending protec provide</t>
@@ -3441,9 +3575,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -3834,7 +3970,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="87">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4044,6 +4180,38 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6774,6 +6942,384 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="53" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="54" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="43" t="s">
+        <v>841</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>919</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="43" t="s">
+        <v>844</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="43" t="s">
+        <v>846</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>923</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>858</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>924</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>862</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
+        <v>472</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
+        <v>352</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="43" t="s">
+        <v>866</v>
+      </c>
+      <c r="E10" s="47" t="n">
+        <f aca="false">COUNTA(A13:A20)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="43" t="s">
+        <v>870</v>
+      </c>
+      <c r="B12" s="43" t="s">
+        <v>697</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>357</v>
+      </c>
+      <c r="D12" s="43" t="s">
+        <v>472</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>352</v>
+      </c>
+      <c r="F12" s="43" t="s">
+        <v>885</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>888</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="B13" s="55" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C13" s="47" t="s">
+        <v>797</v>
+      </c>
+      <c r="D13" s="47" t="s">
+        <v>928</v>
+      </c>
+      <c r="E13" s="47" t="s">
+        <v>798</v>
+      </c>
+      <c r="F13" s="47" t="s">
+        <v>929</v>
+      </c>
+      <c r="G13" s="55" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H13" s="56" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="47" t="s">
+        <v>930</v>
+      </c>
+      <c r="B14" s="55" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C14" s="47" t="s">
+        <v>806</v>
+      </c>
+      <c r="D14" s="47" t="s">
+        <v>931</v>
+      </c>
+      <c r="E14" s="47" t="s">
+        <v>807</v>
+      </c>
+      <c r="F14" s="47" t="s">
+        <v>932</v>
+      </c>
+      <c r="G14" s="55" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H14" s="56" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="47" t="s">
+        <v>933</v>
+      </c>
+      <c r="B15" s="55" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>821</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>934</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>935</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>936</v>
+      </c>
+      <c r="G15" s="55" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H15" s="56" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="B16" s="55" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>814</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>937</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>938</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>939</v>
+      </c>
+      <c r="G16" s="55" t="n">
+        <v>46251</v>
+      </c>
+      <c r="H16" s="56" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="B17" s="55" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C17" s="47" t="s">
+        <v>829</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>940</v>
+      </c>
+      <c r="E17" s="47" t="s">
+        <v>941</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>942</v>
+      </c>
+      <c r="G17" s="55" t="n">
+        <v>46250</v>
+      </c>
+      <c r="H17" s="56" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="B18" s="55" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>943</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>928</v>
+      </c>
+      <c r="E18" s="47" t="s">
+        <v>944</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>945</v>
+      </c>
+      <c r="G18" s="55" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H18" s="56" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="B19" s="55" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C19" s="47" t="s">
+        <v>946</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>947</v>
+      </c>
+      <c r="E19" s="47" t="s">
+        <v>948</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>949</v>
+      </c>
+      <c r="G19" s="55" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H19" s="56" t="n">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="47" t="s">
+        <v>927</v>
+      </c>
+      <c r="B20" s="55" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C20" s="47" t="s">
+        <v>950</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>951</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>952</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>953</v>
+      </c>
+      <c r="G20" s="55" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H20" s="56" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G21" s="57" t="s">
+        <v>610</v>
+      </c>
+      <c r="H21" s="58" t="n">
+        <f aca="false">SUM(H13:H20)</f>
+        <v>217500</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="43" t="s">
+        <v>664</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
+        <v>955</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>956</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -6793,7 +7339,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>917</v>
+        <v>957</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>628</v>
@@ -7027,17 +7573,17 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>919</v>
+        <v>959</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>920</v>
+        <v>960</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>921</v>
+        <v>961</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -7046,19 +7592,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>922</v>
+        <v>962</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>923</v>
+        <v>963</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>864</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>924</v>
+        <v>964</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>648</v>
@@ -7069,19 +7615,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>925</v>
+        <v>965</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>926</v>
+        <v>966</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>864</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>927</v>
+        <v>967</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -7090,17 +7636,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>891</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>928</v>
+        <v>968</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
-        <v>929</v>
+        <v>969</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -7109,7 +7655,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>114</v>
@@ -7117,7 +7663,7 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
-        <v>930</v>
+        <v>970</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -7136,7 +7682,7 @@
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
-        <v>931</v>
+        <v>971</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -7320,7 +7866,317 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="53" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="54" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="43" t="s">
+        <v>841</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>919</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" s="47" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="43" t="s">
+        <v>844</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>921</v>
+      </c>
+      <c r="D5" s="43" t="s">
+        <v>855</v>
+      </c>
+      <c r="E5" s="47" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="43" t="s">
+        <v>846</v>
+      </c>
+      <c r="B6" s="47" t="s">
+        <v>923</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>858</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="s">
+        <v>357</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>924</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>862</v>
+      </c>
+      <c r="E7" s="55" t="n">
+        <v>46255</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
+        <v>472</v>
+      </c>
+      <c r="B8" s="47" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
+        <v>352</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="43" t="s">
+        <v>959</v>
+      </c>
+      <c r="B11" s="43" t="s">
+        <v>962</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>965</v>
+      </c>
+      <c r="D11" s="43" t="s">
+        <v>891</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="47" t="s">
+        <v>720</v>
+      </c>
+      <c r="B12" s="47" t="n">
+        <v>500</v>
+      </c>
+      <c r="C12" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="D12" s="59" t="n">
+        <f aca="false">B12*C12</f>
+        <v>12000</v>
+      </c>
+      <c r="E12" s="47"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="47" t="s">
+        <v>720</v>
+      </c>
+      <c r="B13" s="47" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" s="47" t="n">
+        <v>49</v>
+      </c>
+      <c r="D13" s="59" t="n">
+        <f aca="false">B13*C13</f>
+        <v>4900</v>
+      </c>
+      <c r="E13" s="47"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="47" t="s">
+        <v>720</v>
+      </c>
+      <c r="B14" s="47" t="n">
+        <v>50</v>
+      </c>
+      <c r="C14" s="47" t="n">
+        <v>36</v>
+      </c>
+      <c r="D14" s="59" t="n">
+        <f aca="false">B14*C14</f>
+        <v>1800</v>
+      </c>
+      <c r="E14" s="47"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="47" t="s">
+        <v>720</v>
+      </c>
+      <c r="B15" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="59" t="n">
+        <f aca="false">B15*C15</f>
+        <v>200</v>
+      </c>
+      <c r="E15" s="47"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="47" t="s">
+        <v>720</v>
+      </c>
+      <c r="B16" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C16" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="59" t="n">
+        <f aca="false">B16*C16</f>
+        <v>50</v>
+      </c>
+      <c r="E16" s="47"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="47" t="s">
+        <v>974</v>
+      </c>
+      <c r="B17" s="47" t="n">
+        <v>20</v>
+      </c>
+      <c r="C17" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="59" t="n">
+        <f aca="false">B17*C17</f>
+        <v>200</v>
+      </c>
+      <c r="E17" s="47"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="47" t="s">
+        <v>974</v>
+      </c>
+      <c r="B18" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="59" t="n">
+        <f aca="false">B18*C18</f>
+        <v>100</v>
+      </c>
+      <c r="E18" s="47"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="47" t="s">
+        <v>974</v>
+      </c>
+      <c r="B19" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" s="59" t="n">
+        <f aca="false">B19*C19</f>
+        <v>50</v>
+      </c>
+      <c r="E19" s="47"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="47" t="s">
+        <v>974</v>
+      </c>
+      <c r="B20" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="59" t="n">
+        <f aca="false">B20*C20</f>
+        <v>20</v>
+      </c>
+      <c r="E20" s="47"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="47" t="s">
+        <v>974</v>
+      </c>
+      <c r="B21" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="47" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="59" t="n">
+        <f aca="false">B21*C21</f>
+        <v>10</v>
+      </c>
+      <c r="E21" s="47"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="57" t="s">
+        <v>610</v>
+      </c>
+      <c r="D22" s="60" t="n">
+        <f aca="false">SUM(D12:D21)</f>
+        <v>19330</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="43" t="s">
+        <v>664</v>
+      </c>
+      <c r="B24" s="47" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>955</v>
+      </c>
+      <c r="D26" s="0" t="s">
+        <v>956</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFFF0000"/>
@@ -7330,8 +8186,8 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="53" t="s">
-        <v>932</v>
+      <c r="B2" s="61" t="s">
+        <v>976</v>
       </c>
     </row>
   </sheetData>
@@ -7345,7 +8201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7363,7 +8219,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFFFC000"/>
@@ -7372,7 +8228,7 @@
   <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="54" width="59.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="59.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
@@ -7384,39 +8240,39 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="55" t="s">
-        <v>933</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="57" t="s">
-        <v>934</v>
-      </c>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
+      <c r="A1" s="63" t="s">
+        <v>977</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="65" t="s">
+        <v>978</v>
+      </c>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
     </row>
     <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59" t="s">
-        <v>935</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>936</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>937</v>
-      </c>
-      <c r="E2" s="61" t="s">
-        <v>938</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>939</v>
-      </c>
-      <c r="G2" s="62" t="s">
-        <v>940</v>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67" t="s">
+        <v>979</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>980</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>981</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>982</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>983</v>
+      </c>
+      <c r="G2" s="70" t="s">
+        <v>984</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>5</v>
@@ -7426,10 +8282,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="58" t="s">
-        <v>941</v>
-      </c>
-      <c r="B3" s="59"/>
+      <c r="A3" s="66" t="s">
+        <v>985</v>
+      </c>
+      <c r="B3" s="67"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -7438,141 +8294,141 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63" t="s">
-        <v>942</v>
-      </c>
-      <c r="B4" s="64"/>
+      <c r="A4" s="71" t="s">
+        <v>986</v>
+      </c>
+      <c r="B4" s="72"/>
       <c r="C4" s="4" t="s">
-        <v>943</v>
+        <v>987</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>944</v>
+        <v>988</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>945</v>
+        <v>989</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="63" t="s">
-        <v>947</v>
-      </c>
-      <c r="B5" s="64"/>
+      <c r="A5" s="71" t="s">
+        <v>991</v>
+      </c>
+      <c r="B5" s="72"/>
       <c r="C5" s="4" t="s">
-        <v>948</v>
+        <v>992</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>949</v>
+        <v>993</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>950</v>
+        <v>994</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63" t="s">
-        <v>951</v>
-      </c>
-      <c r="B6" s="64"/>
+      <c r="A6" s="71" t="s">
+        <v>995</v>
+      </c>
+      <c r="B6" s="72"/>
       <c r="C6" s="4" t="s">
-        <v>952</v>
+        <v>996</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>953</v>
+        <v>997</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>954</v>
+        <v>998</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="63" t="s">
-        <v>955</v>
-      </c>
-      <c r="B7" s="64"/>
+      <c r="A7" s="71" t="s">
+        <v>999</v>
+      </c>
+      <c r="B7" s="72"/>
       <c r="C7" s="4" t="s">
-        <v>956</v>
+        <v>1000</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>957</v>
+        <v>1001</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>958</v>
+        <v>1002</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
-        <v>959</v>
-      </c>
-      <c r="B8" s="64"/>
+      <c r="A8" s="71" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B8" s="72"/>
       <c r="C8" s="4" t="s">
-        <v>960</v>
+        <v>1004</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>961</v>
+        <v>1005</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>962</v>
+        <v>1006</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="63" t="s">
-        <v>963</v>
-      </c>
-      <c r="B9" s="64"/>
+      <c r="A9" s="71" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B9" s="72"/>
       <c r="C9" s="4" t="s">
-        <v>964</v>
+        <v>1008</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>965</v>
+        <v>1009</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>966</v>
+        <v>1010</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="63" t="s">
-        <v>967</v>
-      </c>
-      <c r="B10" s="64"/>
+      <c r="A10" s="71" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B10" s="72"/>
       <c r="C10" s="4" t="s">
-        <v>968</v>
+        <v>1012</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>969</v>
+        <v>1013</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>290</v>
@@ -7581,23 +8437,23 @@
         <v>307</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>970</v>
+        <v>1014</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
-        <v>971</v>
-      </c>
-      <c r="B11" s="64"/>
+      <c r="A11" s="71" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B11" s="72"/>
       <c r="C11" s="4" t="s">
-        <v>972</v>
+        <v>1016</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>973</v>
+        <v>1017</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>290</v>
@@ -7606,23 +8462,23 @@
         <v>307</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>974</v>
+        <v>1018</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="63" t="s">
-        <v>975</v>
-      </c>
-      <c r="B12" s="64"/>
+      <c r="A12" s="71" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B12" s="72"/>
       <c r="C12" s="4" t="s">
-        <v>976</v>
+        <v>1020</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>977</v>
+        <v>1021</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>290</v>
@@ -7631,256 +8487,256 @@
         <v>307</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>978</v>
+        <v>1022</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="63" t="s">
-        <v>979</v>
-      </c>
-      <c r="B13" s="64"/>
+      <c r="A13" s="71" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B13" s="72"/>
       <c r="C13" s="4" t="s">
-        <v>980</v>
+        <v>1024</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>981</v>
+        <v>1025</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>982</v>
+        <v>1026</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
-        <v>983</v>
-      </c>
-      <c r="B14" s="64"/>
+      <c r="A14" s="71" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B14" s="72"/>
       <c r="C14" s="4" t="s">
-        <v>984</v>
+        <v>1028</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>985</v>
+        <v>1029</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>986</v>
+        <v>1030</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="63" t="s">
-        <v>987</v>
-      </c>
-      <c r="B15" s="64"/>
+      <c r="A15" s="71" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B15" s="72"/>
       <c r="C15" s="4" t="s">
-        <v>988</v>
+        <v>1032</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>989</v>
+        <v>1033</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>946</v>
-      </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="65" t="s">
-        <v>991</v>
-      </c>
-      <c r="B16" s="64"/>
+      <c r="A16" s="73" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B16" s="72"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>992</v>
+        <v>1036</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="63" t="s">
-        <v>993</v>
-      </c>
-      <c r="B17" s="64"/>
+      <c r="A17" s="71" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B17" s="72"/>
       <c r="C17" s="4" t="s">
-        <v>994</v>
+        <v>1038</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>995</v>
+        <v>1039</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
         <v>111</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>996</v>
+        <v>1040</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="63" t="s">
-        <v>997</v>
-      </c>
-      <c r="B18" s="64"/>
+      <c r="A18" s="71" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B18" s="72"/>
       <c r="C18" s="4" t="s">
-        <v>998</v>
+        <v>1042</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>999</v>
+        <v>1043</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
-        <v>1000</v>
+        <v>1044</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="65" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B19" s="64"/>
+      <c r="A19" s="73" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B19" s="72"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>1002</v>
+        <v>1046</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="66" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B20" s="64"/>
+      <c r="A20" s="74" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B20" s="72"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>1004</v>
+        <v>1048</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="63" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B21" s="59"/>
+      <c r="A21" s="71" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B21" s="67"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4" t="s">
-        <v>1006</v>
+        <v>1050</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>1007</v>
+        <v>1051</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B22" s="59"/>
+      <c r="A22" s="71" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B22" s="67"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1010</v>
+        <v>1054</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B23" s="59"/>
+      <c r="A23" s="71" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B23" s="67"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>1012</v>
+        <v>1056</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>1013</v>
+        <v>1057</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="63" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B24" s="59"/>
+      <c r="A24" s="71" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B24" s="67"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>1015</v>
+        <v>1059</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1016</v>
+        <v>1060</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="66" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B25" s="67"/>
+      <c r="A25" s="74" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B25" s="75"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>1018</v>
+        <v>1062</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="68"/>
+      <c r="A26" s="76"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
@@ -7904,7 +8760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFFFC000"/>
@@ -7913,7 +8769,7 @@
   <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="54" width="59.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="59.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="69.29"/>
@@ -7925,37 +8781,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="55" t="s">
-        <v>933</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
+      <c r="A1" s="63" t="s">
+        <v>977</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
     </row>
     <row r="2" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59" t="s">
-        <v>935</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>936</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>937</v>
-      </c>
-      <c r="E2" s="61" t="s">
-        <v>938</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>939</v>
-      </c>
-      <c r="G2" s="62" t="s">
-        <v>940</v>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67" t="s">
+        <v>979</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>980</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>981</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>982</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>983</v>
+      </c>
+      <c r="G2" s="70" t="s">
+        <v>984</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>5</v>
@@ -7965,10 +8821,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="58" t="s">
-        <v>941</v>
-      </c>
-      <c r="B3" s="59"/>
+      <c r="A3" s="66" t="s">
+        <v>985</v>
+      </c>
+      <c r="B3" s="67"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -7978,141 +8834,141 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63" t="s">
-        <v>942</v>
-      </c>
-      <c r="B4" s="64"/>
+      <c r="A4" s="71" t="s">
+        <v>986</v>
+      </c>
+      <c r="B4" s="72"/>
       <c r="C4" s="4" t="s">
-        <v>943</v>
+        <v>987</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>944</v>
+        <v>988</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>945</v>
+        <v>989</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="63" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B5" s="64"/>
+      <c r="A5" s="71" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B5" s="72"/>
       <c r="C5" s="4" t="s">
-        <v>948</v>
+        <v>992</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>949</v>
+        <v>993</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>950</v>
+        <v>994</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B6" s="64"/>
+      <c r="A6" s="71" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B6" s="72"/>
       <c r="C6" s="4" t="s">
-        <v>952</v>
+        <v>996</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>953</v>
+        <v>997</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>954</v>
+        <v>998</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="63" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B7" s="64"/>
+      <c r="A7" s="71" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B7" s="72"/>
       <c r="C7" s="4" t="s">
-        <v>956</v>
+        <v>1000</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>957</v>
+        <v>1001</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>958</v>
+        <v>1002</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B8" s="64"/>
+      <c r="A8" s="71" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B8" s="72"/>
       <c r="C8" s="4" t="s">
-        <v>1023</v>
+        <v>1067</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1024</v>
+        <v>1068</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>1025</v>
+        <v>1069</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="63" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B9" s="64"/>
+      <c r="A9" s="71" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B9" s="72"/>
       <c r="C9" s="4" t="s">
-        <v>1027</v>
+        <v>1071</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1028</v>
+        <v>1072</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>1029</v>
+        <v>1073</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="63" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B10" s="64"/>
+      <c r="A10" s="71" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B10" s="72"/>
       <c r="C10" s="4" t="s">
-        <v>1031</v>
+        <v>1075</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1030</v>
+        <v>1074</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>290</v>
@@ -8121,65 +8977,65 @@
         <v>307</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>970</v>
+        <v>1014</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B11" s="64"/>
+      <c r="A11" s="71" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B11" s="72"/>
       <c r="C11" s="4" t="s">
-        <v>1033</v>
+        <v>1077</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E11" s="69"/>
-      <c r="F11" s="70"/>
+        <v>1078</v>
+      </c>
+      <c r="E11" s="77"/>
+      <c r="F11" s="78"/>
       <c r="G11" s="4" t="s">
-        <v>1035</v>
+        <v>1079</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="63" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B12" s="64"/>
+      <c r="A12" s="71" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B12" s="72"/>
       <c r="C12" s="4" t="s">
-        <v>964</v>
+        <v>1008</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>965</v>
+        <v>1009</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>966</v>
+        <v>1010</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="63" t="s">
-        <v>975</v>
-      </c>
-      <c r="B13" s="64"/>
+      <c r="A13" s="71" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B13" s="72"/>
       <c r="C13" s="4" t="s">
-        <v>976</v>
+        <v>1020</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1037</v>
+        <v>1081</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>290</v>
@@ -8188,400 +9044,400 @@
         <v>307</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>978</v>
+        <v>1022</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
-        <v>979</v>
-      </c>
-      <c r="B14" s="64"/>
+      <c r="A14" s="71" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B14" s="72"/>
       <c r="C14" s="4" t="s">
-        <v>980</v>
+        <v>1024</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1038</v>
+        <v>1082</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>982</v>
+        <v>1026</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="63" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B15" s="64"/>
+      <c r="A15" s="71" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B15" s="72"/>
       <c r="C15" s="4" t="s">
-        <v>1040</v>
+        <v>1084</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1041</v>
+        <v>1085</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>1042</v>
+        <v>1086</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B16" s="64"/>
+      <c r="A16" s="71" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B16" s="72"/>
       <c r="C16" s="4" t="s">
-        <v>1044</v>
+        <v>1088</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1045</v>
+        <v>1089</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>1046</v>
+        <v>1090</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="63" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B17" s="64"/>
+      <c r="A17" s="71" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B17" s="72"/>
       <c r="C17" s="4" t="s">
-        <v>1048</v>
+        <v>1092</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1049</v>
+        <v>1093</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
-        <v>1050</v>
+        <v>1094</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="63" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B18" s="64"/>
+      <c r="A18" s="71" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B18" s="72"/>
       <c r="C18" s="4" t="s">
-        <v>1052</v>
+        <v>1096</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1053</v>
+        <v>1097</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
-        <v>1054</v>
+        <v>1098</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="63" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B19" s="64"/>
+      <c r="A19" s="71" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B19" s="72"/>
       <c r="C19" s="4" t="s">
-        <v>1056</v>
+        <v>1100</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1057</v>
+        <v>1101</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="4" t="s">
-        <v>1058</v>
+        <v>1102</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="63" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B20" s="64"/>
+      <c r="A20" s="71" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B20" s="72"/>
       <c r="C20" s="4" t="s">
-        <v>1060</v>
+        <v>1104</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1061</v>
+        <v>1105</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4" t="s">
-        <v>1062</v>
+        <v>1106</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="63" t="s">
-        <v>987</v>
-      </c>
-      <c r="B21" s="64"/>
+      <c r="A21" s="71" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B21" s="72"/>
       <c r="C21" s="4" t="s">
-        <v>988</v>
+        <v>1032</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1063</v>
+        <v>1107</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>946</v>
-      </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="65" t="s">
-        <v>991</v>
-      </c>
-      <c r="B22" s="64"/>
+      <c r="A22" s="73" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B22" s="72"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>1064</v>
+        <v>1108</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63" t="s">
-        <v>993</v>
-      </c>
-      <c r="B23" s="64"/>
+      <c r="A23" s="71" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B23" s="72"/>
       <c r="C23" s="4" t="s">
-        <v>994</v>
+        <v>1038</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>995</v>
+        <v>1039</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4" t="s">
         <v>111</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>996</v>
+        <v>1040</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="65" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B24" s="64"/>
+      <c r="A24" s="73" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B24" s="72"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
       <c r="H24" s="4" t="s">
-        <v>1065</v>
+        <v>1109</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B25" s="72"/>
+      <c r="A25" s="79" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B25" s="80"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
       <c r="H25" s="4" t="s">
-        <v>1004</v>
+        <v>1048</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="73" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B26" s="74"/>
+      <c r="A26" s="81" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B26" s="82"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>1067</v>
+        <v>1111</v>
       </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="73" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B27" s="75"/>
+      <c r="A27" s="81" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B27" s="83"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>1068</v>
+        <v>1112</v>
       </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="73" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B28" s="74"/>
+      <c r="A28" s="81" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B28" s="82"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>1070</v>
+        <v>1114</v>
       </c>
       <c r="I28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="73" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B29" s="75"/>
+      <c r="A29" s="81" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B29" s="83"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>1071</v>
+        <v>1115</v>
       </c>
       <c r="I29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="73" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B30" s="75"/>
+      <c r="A30" s="81" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B30" s="83"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="4" t="s">
-        <v>1073</v>
+        <v>1117</v>
       </c>
       <c r="I30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="73" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B31" s="75"/>
+      <c r="A31" s="81" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B31" s="83"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="4" t="s">
-        <v>1074</v>
+        <v>1118</v>
       </c>
       <c r="I31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="73" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B32" s="74"/>
+      <c r="A32" s="81" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B32" s="82"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="4" t="s">
-        <v>1076</v>
+        <v>1120</v>
       </c>
       <c r="I32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="73" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B33" s="75"/>
+      <c r="A33" s="81" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B33" s="83"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="4" t="s">
-        <v>1077</v>
+        <v>1121</v>
       </c>
       <c r="I33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="73" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B34" s="76"/>
+      <c r="A34" s="81" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B34" s="84"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="4" t="s">
-        <v>1078</v>
+        <v>1122</v>
       </c>
       <c r="I34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="68"/>
+      <c r="A35" s="76"/>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
     </row>
@@ -8604,7 +9460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FFFFC000"/>
@@ -8613,7 +9469,7 @@
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="54" width="59.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="59.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="61.29"/>
@@ -8624,37 +9480,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="55" t="s">
-        <v>933</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
+      <c r="A1" s="63" t="s">
+        <v>977</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
     </row>
     <row r="2" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59" t="s">
-        <v>935</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>936</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>937</v>
-      </c>
-      <c r="E2" s="61" t="s">
-        <v>938</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>939</v>
-      </c>
-      <c r="G2" s="62" t="s">
-        <v>940</v>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67" t="s">
+        <v>979</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>980</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>981</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>982</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>983</v>
+      </c>
+      <c r="G2" s="70" t="s">
+        <v>984</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>5</v>
@@ -8664,10 +9520,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="58" t="s">
-        <v>941</v>
-      </c>
-      <c r="B3" s="59"/>
+      <c r="A3" s="66" t="s">
+        <v>985</v>
+      </c>
+      <c r="B3" s="67"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -8677,162 +9533,162 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63" t="s">
-        <v>942</v>
-      </c>
-      <c r="B4" s="64"/>
+      <c r="A4" s="71" t="s">
+        <v>986</v>
+      </c>
+      <c r="B4" s="72"/>
       <c r="C4" s="4" t="s">
-        <v>943</v>
+        <v>987</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>944</v>
+        <v>988</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>945</v>
+        <v>989</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="63" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B5" s="64"/>
+      <c r="A5" s="71" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B5" s="72"/>
       <c r="C5" s="4" t="s">
-        <v>948</v>
+        <v>992</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>949</v>
+        <v>993</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>950</v>
+        <v>994</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B6" s="64"/>
+      <c r="A6" s="71" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B6" s="72"/>
       <c r="C6" s="4" t="s">
-        <v>952</v>
+        <v>996</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>953</v>
+        <v>997</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>954</v>
+        <v>998</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="63" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B7" s="64"/>
+      <c r="A7" s="71" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B7" s="72"/>
       <c r="C7" s="4" t="s">
-        <v>956</v>
+        <v>1000</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>957</v>
+        <v>1001</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>958</v>
+        <v>1002</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B8" s="64"/>
+      <c r="A8" s="71" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B8" s="72"/>
       <c r="C8" s="4" t="s">
-        <v>1027</v>
+        <v>1071</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1028</v>
+        <v>1072</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>1029</v>
+        <v>1073</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="63" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B9" s="64"/>
+      <c r="A9" s="71" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B9" s="72"/>
       <c r="C9" s="4" t="s">
-        <v>1033</v>
+        <v>1077</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1034</v>
-      </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="70"/>
+        <v>1078</v>
+      </c>
+      <c r="E9" s="77"/>
+      <c r="F9" s="78"/>
       <c r="G9" s="4" t="s">
-        <v>1035</v>
+        <v>1079</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="63" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B10" s="64"/>
+      <c r="A10" s="71" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B10" s="72"/>
       <c r="C10" s="4" t="s">
-        <v>964</v>
+        <v>1008</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>965</v>
+        <v>1009</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>966</v>
+        <v>1010</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
-        <v>975</v>
-      </c>
-      <c r="B11" s="64"/>
+      <c r="A11" s="71" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B11" s="72"/>
       <c r="C11" s="4" t="s">
-        <v>976</v>
+        <v>1020</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1037</v>
+        <v>1081</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>290</v>
@@ -8841,880 +9697,307 @@
         <v>307</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>978</v>
+        <v>1022</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="63" t="s">
-        <v>979</v>
-      </c>
-      <c r="B12" s="64"/>
+      <c r="A12" s="71" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B12" s="72"/>
       <c r="C12" s="4" t="s">
-        <v>980</v>
+        <v>1024</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1038</v>
+        <v>1082</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>982</v>
+        <v>1026</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="63" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B13" s="64"/>
+      <c r="A13" s="71" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B13" s="72"/>
       <c r="C13" s="4" t="s">
-        <v>1040</v>
+        <v>1084</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1041</v>
+        <v>1085</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>1042</v>
+        <v>1086</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B14" s="64"/>
+      <c r="A14" s="71" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B14" s="72"/>
       <c r="C14" s="4" t="s">
-        <v>1044</v>
+        <v>1088</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1045</v>
+        <v>1089</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>1046</v>
+        <v>1090</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="63" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B15" s="64"/>
+      <c r="A15" s="71" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B15" s="72"/>
       <c r="C15" s="4" t="s">
-        <v>1048</v>
+        <v>1092</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1049</v>
+        <v>1093</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>1050</v>
+        <v>1094</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B16" s="64"/>
+      <c r="A16" s="71" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B16" s="72"/>
       <c r="C16" s="4" t="s">
-        <v>1060</v>
+        <v>1104</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1061</v>
+        <v>1105</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>1062</v>
+        <v>1106</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="63" t="s">
-        <v>987</v>
-      </c>
-      <c r="B17" s="64"/>
+      <c r="A17" s="71" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B17" s="72"/>
       <c r="C17" s="4" t="s">
-        <v>988</v>
+        <v>1032</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1063</v>
+        <v>1107</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>990</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>946</v>
-      </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="65" t="s">
-        <v>991</v>
-      </c>
-      <c r="B18" s="64"/>
+      <c r="A18" s="73" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B18" s="72"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>1080</v>
+        <v>1124</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="63" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B19" s="64"/>
+      <c r="A19" s="71" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B19" s="72"/>
       <c r="C19" s="4" t="s">
-        <v>994</v>
+        <v>1038</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>995</v>
+        <v>1039</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
         <v>111</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>996</v>
+        <v>1040</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>946</v>
+        <v>990</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="65" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B20" s="64"/>
+      <c r="A20" s="73" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B20" s="72"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>1082</v>
+        <v>1126</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="66" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B21" s="64"/>
+      <c r="A21" s="74" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B21" s="72"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>1004</v>
+        <v>1048</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="66" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B22" s="59"/>
+      <c r="A22" s="74" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B22" s="67"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>1006</v>
+        <v>1050</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1007</v>
+        <v>1051</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="66" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B23" s="59"/>
+      <c r="A23" s="74" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B23" s="67"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>1009</v>
+        <v>1053</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>1010</v>
+        <v>1054</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="66" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B24" s="59"/>
+      <c r="A24" s="74" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B24" s="67"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>1012</v>
+        <v>1056</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1013</v>
+        <v>1057</v>
       </c>
       <c r="I24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="63" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B25" s="59"/>
+      <c r="A25" s="71" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B25" s="67"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
-        <v>1015</v>
+        <v>1059</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>1016</v>
+        <v>1060</v>
       </c>
       <c r="I25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="66" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B26" s="67"/>
+      <c r="A26" s="74" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B26" s="75"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>1083</v>
+        <v>1127</v>
       </c>
       <c r="I26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="68"/>
+      <c r="A27" s="76"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
+      <c r="E27" s="85"/>
+      <c r="F27" s="85"/>
       <c r="G27" s="17"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FFFFC000"/>
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:I29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="54" width="59.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="57.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="27.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.14"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="55" t="s">
-        <v>933</v>
-      </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-    </row>
-    <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59" t="s">
-        <v>935</v>
-      </c>
-      <c r="C2" s="60" t="s">
-        <v>936</v>
-      </c>
-      <c r="D2" s="60" t="s">
-        <v>937</v>
-      </c>
-      <c r="E2" s="61" t="s">
-        <v>938</v>
-      </c>
-      <c r="F2" s="61" t="s">
-        <v>939</v>
-      </c>
-      <c r="G2" s="62" t="s">
-        <v>940</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I2" s="14" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="58" t="s">
-        <v>941</v>
-      </c>
-      <c r="B3" s="59"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63" t="s">
-        <v>942</v>
-      </c>
-      <c r="B4" s="64"/>
-      <c r="C4" s="4" t="s">
-        <v>943</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>944</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
-        <v>945</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="63" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="4" t="s">
-        <v>948</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>949</v>
-      </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
-        <v>950</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="63" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="4" t="s">
-        <v>952</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>953</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>954</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="63" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>957</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>958</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="63" t="s">
-        <v>959</v>
-      </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="4" t="s">
-        <v>960</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>961</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="63" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="4" t="s">
-        <v>964</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>965</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
-        <v>966</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="63" t="s">
-        <v>967</v>
-      </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="4" t="s">
-        <v>968</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>970</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="63" t="s">
-        <v>971</v>
-      </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="4" t="s">
-        <v>972</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="63" t="s">
-        <v>975</v>
-      </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="4" t="s">
-        <v>976</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>978</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="63" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="4" t="s">
-        <v>1088</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>1090</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="63" t="s">
-        <v>979</v>
-      </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="4" t="s">
-        <v>980</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>981</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
-        <v>982</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I14" s="4"/>
-    </row>
-    <row r="15" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="63" t="s">
-        <v>983</v>
-      </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="4" t="s">
-        <v>984</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>1091</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4" t="s">
-        <v>986</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="63" t="s">
-        <v>987</v>
-      </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="4" t="s">
-        <v>988</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4" t="s">
-        <v>990</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="65" t="s">
-        <v>991</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4" t="s">
-        <v>1093</v>
-      </c>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="63" t="s">
-        <v>993</v>
-      </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="4" t="s">
-        <v>994</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>995</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>996</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="63" t="s">
-        <v>1094</v>
-      </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="4" t="s">
-        <v>998</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>1095</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4" t="s">
-        <v>1000</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="65" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B20" s="64"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4" t="s">
-        <v>1096</v>
-      </c>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="66" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4" t="s">
-        <v>1004</v>
-      </c>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="63" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B22" s="59"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>1007</v>
-      </c>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="63" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4" t="s">
-        <v>1009</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>1010</v>
-      </c>
-      <c r="I23" s="4"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="63" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B24" s="59"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>1013</v>
-      </c>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="63" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I25" s="4"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="66" t="s">
-        <v>1017</v>
-      </c>
-      <c r="B26" s="67"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I26" s="4"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="68"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-    </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="78"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-    </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="78"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10879,6 +11162,579 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFFFC000"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="59.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="57.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="23.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="27.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.14"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="63" t="s">
+        <v>977</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+    </row>
+    <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67" t="s">
+        <v>979</v>
+      </c>
+      <c r="C2" s="68" t="s">
+        <v>980</v>
+      </c>
+      <c r="D2" s="68" t="s">
+        <v>981</v>
+      </c>
+      <c r="E2" s="69" t="s">
+        <v>982</v>
+      </c>
+      <c r="F2" s="69" t="s">
+        <v>983</v>
+      </c>
+      <c r="G2" s="70" t="s">
+        <v>984</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="66" t="s">
+        <v>985</v>
+      </c>
+      <c r="B3" s="67"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="71" t="s">
+        <v>986</v>
+      </c>
+      <c r="B4" s="72"/>
+      <c r="C4" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="71" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="71" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B6" s="72"/>
+      <c r="C6" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="71" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B7" s="72"/>
+      <c r="C7" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="71" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B8" s="72"/>
+      <c r="C8" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="71" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B9" s="72"/>
+      <c r="C9" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="71" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B10" s="72"/>
+      <c r="C10" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="71" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B11" s="72"/>
+      <c r="C11" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="71" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B12" s="72"/>
+      <c r="C12" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="71" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B13" s="72"/>
+      <c r="C13" s="4" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="71" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B14" s="72"/>
+      <c r="C14" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="71" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B15" s="72"/>
+      <c r="C15" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="71" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B16" s="72"/>
+      <c r="C16" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="73" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B17" s="72"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I17" s="4"/>
+    </row>
+    <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="71" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B18" s="72"/>
+      <c r="C18" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="71" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B19" s="72"/>
+      <c r="C19" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="73" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B20" s="72"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="74" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B21" s="72"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="71" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B22" s="67"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I22" s="4"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="71" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B23" s="67"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>1054</v>
+      </c>
+      <c r="I23" s="4"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="71" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B24" s="67"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="71" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B25" s="67"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>1060</v>
+      </c>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="74" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B26" s="75"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I26" s="4"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="76"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+    </row>
+    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="86"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="86"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">

--- a/PA_communication_mapping_tables_20261021_1.xlsx
+++ b/PA_communication_mapping_tables_20261021_1.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="1141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2650" uniqueCount="1125">
   <si>
     <t xml:space="preserve">Sr No</t>
   </si>
@@ -2453,211 +2453,160 @@
     <t xml:space="preserve">1F4E79 dark blue (bands), 595959 grey (footer), FFFFFF white (text on bands).</t>
   </si>
   <si>
-    <t xml:space="preserve">Collection Receipt - Example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illustrative values. Table lines are the sample values in the v5 template; header values are made up for illustration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BCP field</t>
+    <t xml:space="preserve">Protec General Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[QR CODE - scan to verify]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLLECTION RECEIPT</t>
   </si>
   <si>
     <t xml:space="preserve">RCT-1106-26-00004521</t>
   </si>
   <si>
-    <t xml:space="preserve">Collection.ReceiptNo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27-10-2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Customer</t>
   </si>
   <si>
-    <t xml:space="preserve">Collection.PayerPayeeType (confirm)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1106</t>
   </si>
   <si>
-    <t xml:space="preserve">Collection.BranchCode</t>
-  </si>
-  <si>
     <t xml:space="preserve">CUST-000123</t>
   </si>
   <si>
     <t xml:space="preserve">AGT-004567</t>
   </si>
   <si>
-    <t xml:space="preserve">Collection.ChannelCode / leader agent</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ravi Kumar</t>
   </si>
   <si>
-    <t xml:space="preserve">3,97,500.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum of CollectionDetail.Amount (lines below)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rupees Three Lakh Ninety Seven Thousand Five Hundred Only</t>
   </si>
   <si>
-    <t xml:space="preserve">Derived from Amount Collected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collection lines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch IFSC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premium - New Business</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor Private Car</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PQ-1106-26-00000540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,00,000.00</t>
+    <t xml:space="preserve">Product / LoB
+Reference No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Name
+Branch IFSC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instrument / UTR
+/ Txn Ref No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium -
+New Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor Private Car
+PQ-1106-26-00000540</t>
   </si>
   <si>
     <t xml:space="preserve">Cheque</t>
   </si>
   <si>
-    <t xml:space="preserve">State Bank of India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SBIN0000123</t>
+    <t xml:space="preserve">State Bank of India
+SBIN0000123</t>
   </si>
   <si>
     <t xml:space="preserve">0012345</t>
   </si>
   <si>
-    <t xml:space="preserve">03-06-2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Premium - Renewal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health Individual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POL-1106-26-00001234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25,000.00</t>
+    <t xml:space="preserve">Premium -
+Renewal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health Individual
+POL-1106-26-00001234</t>
   </si>
   <si>
     <t xml:space="preserve">NEFT</t>
   </si>
   <si>
-    <t xml:space="preserve">HDFC Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDFC0002323</t>
+    <t xml:space="preserve">HDFC Bank
+HDFC0002323</t>
   </si>
   <si>
     <t xml:space="preserve">HDFCN26102700123</t>
   </si>
   <si>
-    <t xml:space="preserve">Endorsement Premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire &amp; Allied Perils</t>
-  </si>
-  <si>
-    <t xml:space="preserve">END-1106-26-00000087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4,500.00</t>
+    <t xml:space="preserve">Endorsement
+Premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire &amp; Allied Perils
+END-1106-26-00000087</t>
   </si>
   <si>
     <t xml:space="preserve">UPI</t>
   </si>
   <si>
-    <t xml:space="preserve">ICICI Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICIC000014</t>
+    <t xml:space="preserve">ICICI Bank
+ICIC000014</t>
   </si>
   <si>
     <t xml:space="preserve">6012345678</t>
   </si>
   <si>
-    <t xml:space="preserve">Claim Recovery - Salvage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLM-1106-26-00000311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,000.00</t>
+    <t xml:space="preserve">Claim Recovery -
+Salvage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor Private Car
+CLM-1106-26-00000311</t>
   </si>
   <si>
     <t xml:space="preserve">RTGS</t>
   </si>
   <si>
-    <t xml:space="preserve">Axis Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UTIB000016</t>
+    <t xml:space="preserve">Axis Bank
+UTIB000016</t>
   </si>
   <si>
     <t xml:space="preserve">AXISR26102700456</t>
   </si>
   <si>
-    <t xml:space="preserve">26-10-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim Recovery - Subrogation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marine Cargo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLM-1106-26-00000142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,50,000.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank of Baroda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOB00100234</t>
+    <t xml:space="preserve">Claim Recovery -
+Subrogation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marine Cargo
+CLM-1106-26-00000142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank of Baroda
+BOB00100234</t>
   </si>
   <si>
     <t xml:space="preserve">BARBN26102600789</t>
   </si>
   <si>
-    <t xml:space="preserve">Policy TranType (NB/RB/Endo) or Claim ARAP type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proposal/Policy/Endorsement/Claim No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collection.BankName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collection.IFSCCode (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collection.InstrumentNo / UTR (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collection.InstrumentDate (confirm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total of lines (check)</t>
+    <t xml:space="preserve">This is a system-generated receipt and does not require a signature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: This receipt is issued as an acknowledgement of the deposit received by the Company and is subject to realization of the Cheque/Demand Draft/electronic payment. The assumption of risk and commencement of coverage shall be subject to evaluation and acceptance of the proposal by the Company. Upon acceptance of the proposal and issuance of the policy, the deposit shall be appropriated towards the applicable premium. Should the proposal be declined by the Company or withdrawn by the applicant, the deposit will be refunded in full.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[COMPANY NAME]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Registered Office: &lt;Address&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIN: XXXXXXXXXXXXXXXXXXXXX   |   IRDAI Regn. No.: XXX   |   GSTIN: XXXXXXXXXXXXXXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Care (Toll-free): XXXXXXXXXX   |   Claims: XXXXXXXXXX   |   Email: XXXXXXXX   |   Website: www.XXXXXXXX.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grievances: Grievance Officer - &lt;email / phone&gt;   |   IRDAI Bima Bharosa: bimabharosa.irdai.gov.in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify this receipt: scan the QR code or visit www.XXXXXXXX.com/verify-receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source: GI_Collection_Receipt_Template_v5.docx (logo, layout, wording, sample lines). Header values are illustrative. Placeholders (XXXX, &lt;Address&gt;, QR) are as in the template, to be provided by Protec. Font: Metropolis.</t>
   </si>
   <si>
     <t xml:space="preserve">Document Field (Cheque Deposit Slip)</t>
@@ -2898,13 +2847,7 @@
     <t xml:space="preserve">Handlebars template from the Excel slip.</t>
   </si>
   <si>
-    <t xml:space="preserve">Cheque Deposit Slip - Example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account details, instrument types and Statement values are from DepositSlipSample.xlsx. Bank, cheque number and amount values are illustrative (blank in the sample).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Protec Insurance</t>
+    <t xml:space="preserve">Name of Account Holder : Protec Insurance</t>
   </si>
   <si>
     <t xml:space="preserve">500100</t>
@@ -2913,7 +2856,7 @@
     <t xml:space="preserve">Current Account</t>
   </si>
   <si>
-    <t xml:space="preserve">Andheri (East) branch (from India Branch module)</t>
+    <t xml:space="preserve">Andheri (East) branch</t>
   </si>
   <si>
     <t xml:space="preserve">00012345678900</t>
@@ -2922,33 +2865,51 @@
     <t xml:space="preserve">ICICI Bank Ltd.</t>
   </si>
   <si>
-    <t xml:space="preserve">Andheri (East)</t>
+    <t xml:space="preserve">Andheri (East) </t>
   </si>
   <si>
     <t xml:space="preserve">ICICI00001234</t>
   </si>
   <si>
+    <t xml:space="preserve">Total Number of Instruments : </t>
+  </si>
+  <si>
     <t xml:space="preserve">Local Cheque</t>
   </si>
   <si>
+    <t xml:space="preserve">State Bank of India</t>
+  </si>
+  <si>
     <t xml:space="preserve">Andheri</t>
   </si>
   <si>
+    <t xml:space="preserve">SBIN0000123</t>
+  </si>
+  <si>
     <t xml:space="preserve">000101</t>
   </si>
   <si>
     <t xml:space="preserve">Outstation Cheque</t>
   </si>
   <si>
+    <t xml:space="preserve">HDFC Bank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pune</t>
   </si>
   <si>
+    <t xml:space="preserve">HDFC0002323</t>
+  </si>
+  <si>
     <t xml:space="preserve">000202</t>
   </si>
   <si>
     <t xml:space="preserve">Demand Draft</t>
   </si>
   <si>
+    <t xml:space="preserve">Axis Bank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Chennai</t>
   </si>
   <si>
@@ -2958,6 +2919,9 @@
     <t xml:space="preserve">DD3003</t>
   </si>
   <si>
+    <t xml:space="preserve">ICICI Bank</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bandra</t>
   </si>
   <si>
@@ -2967,6 +2931,9 @@
     <t xml:space="preserve">000404</t>
   </si>
   <si>
+    <t xml:space="preserve">Bank of Baroda</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dadar</t>
   </si>
   <si>
@@ -3012,10 +2979,19 @@
     <t xml:space="preserve">Indian Rupees Two Lakh Seventeen Thousand Five Hundred and Paisa Zero ONLY</t>
   </si>
   <si>
-    <t xml:space="preserve">Signature and Stamp - Protec General Insurance / Date: ____</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Signature and Stamp - Bank Collection Agent / Date: ____</t>
+    <t xml:space="preserve">Signature and Stamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protec General Insurance </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Collection Agent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date :</t>
   </si>
   <si>
     <t xml:space="preserve">Document Field (Cash Deposit Slip)</t>
@@ -3061,12 +3037,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sum of denomination amounts; must equal Collection.Amount for the statement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash Deposit Slip - Example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All values (account details, denominations, pieces, Statement 1001) are from DepositSlipSample.xlsx.</t>
   </si>
   <si>
     <t xml:space="preserve">Coins</t>
@@ -3575,13 +3545,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;₹ &quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0&quot;  X&quot;"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3675,23 +3646,75 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Metropolis"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="Calibri"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Metropolis"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF595959"/>
+      <name val="Metropolis"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Metropolis"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <name val="Metropolis"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="8.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Metropolis"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
+      <sz val="8"/>
+      <name val="Metropolis"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="7.5"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Metropolis"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="7.5"/>
+      <color rgb="FF595959"/>
+      <name val="Metropolis"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF595959"/>
+      <sz val="9"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -3699,8 +3722,9 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -3735,14 +3759,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Aptos"/>
@@ -3750,7 +3766,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3760,7 +3776,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -3777,24 +3793,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.05"/>
+        <bgColor rgb="FFDDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFA6A6A6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="40">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -3904,6 +3938,305 @@
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FF8EAADB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF8EAADB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF8EAADB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF8EAADB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.3999"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="0.3999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="3" tint="0.3999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="3" tint="0.3999"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.3999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color theme="3" tint="0.3999"/>
+      </right>
+      <top style="thin">
+        <color theme="3" tint="0.3999"/>
+      </top>
+      <bottom style="thin">
+        <color theme="3" tint="0.3999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="-0.25"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="-0.25"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-0.15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.15"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="1" tint="0.0499"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.0499"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.35"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top style="thin">
+        <color theme="1" tint="0.0499"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="-0.25"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="-0.25"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="1" tint="0.0499"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.35"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.35"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.35"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.35"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.15"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.15"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.15"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="1" tint="0.0499"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.35"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.35"/>
+      </top>
+      <bottom style="thin">
+        <color theme="1" tint="0.0499"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.15"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top style="double">
+        <color theme="1" tint="0.3499"/>
+      </top>
+      <bottom style="double">
+        <color theme="1" tint="0.3499"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color theme="0" tint="-0.15"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.15"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.15"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.15"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="medium"/>
       <right style="medium"/>
       <top style="medium"/>
@@ -3970,7 +4303,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="132">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4163,67 +4496,247 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="6" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="9" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4231,15 +4744,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="8" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4247,67 +4760,67 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="5" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="8" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4315,7 +4828,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4363,15 +4876,15 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF7F7F7F"/>
+      <rgbColor rgb="FF8EAADB"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF2F2F2"/>
+      <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF376092"/>
+      <rgbColor rgb="FFD9D9D9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -4387,22 +4900,22 @@
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FFFCE4D6"/>
+      <rgbColor rgb="FF558ED5"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF92D050"/>
       <rgbColor rgb="FFFFC000"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF595959"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FFA6A6A6"/>
+      <rgbColor rgb="FF1F4E78"/>
       <rgbColor rgb="FF00B050"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF0D0D0D"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
+      <rgbColor rgb="FF1F4E79"/>
       <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
@@ -4411,6 +4924,48 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1005480</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>428400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="0" name="Image 1" descr="Picture"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="1428480" cy="428400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5813,480 +6368,450 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
+    <row r="1" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="48"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49" t="s">
         <v>770</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="50" t="s">
         <v>771</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
+    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="51" t="s">
         <v>772</v>
       </c>
-      <c r="B4" s="43" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="52" t="s">
+        <v>638</v>
+      </c>
+      <c r="B5" s="52"/>
+      <c r="C5" s="48" t="s">
         <v>773</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="D5" s="48"/>
+      <c r="E5" s="52" t="s">
+        <v>642</v>
+      </c>
+      <c r="F5" s="52"/>
+      <c r="G5" s="53" t="n">
+        <v>46322</v>
+      </c>
+      <c r="H5" s="53"/>
+    </row>
+    <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="52" t="s">
+        <v>645</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="48" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="47" t="s">
-        <v>638</v>
-      </c>
-      <c r="B5" s="47" t="s">
+      <c r="D6" s="48"/>
+      <c r="E6" s="52" t="s">
+        <v>649</v>
+      </c>
+      <c r="F6" s="52"/>
+      <c r="G6" s="48" t="s">
         <v>775</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="H6" s="48"/>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="52" t="s">
+        <v>653</v>
+      </c>
+      <c r="B7" s="52"/>
+      <c r="C7" s="48" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="47" t="s">
-        <v>642</v>
-      </c>
-      <c r="B6" s="47" t="s">
+      <c r="D7" s="48"/>
+      <c r="E7" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="52"/>
+      <c r="G7" s="48" t="s">
         <v>777</v>
       </c>
-      <c r="C6" s="47" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
-        <v>645</v>
-      </c>
-      <c r="B7" s="47" t="s">
+      <c r="H7" s="48"/>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="52" t="s">
+        <v>659</v>
+      </c>
+      <c r="B8" s="52"/>
+      <c r="C8" s="48" t="s">
         <v>778</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="52" t="s">
+        <v>661</v>
+      </c>
+      <c r="B9" s="52"/>
+      <c r="C9" s="54" t="n">
+        <f aca="false">D18</f>
+        <v>397500</v>
+      </c>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="52" t="s">
+        <v>664</v>
+      </c>
+      <c r="B10" s="52"/>
+      <c r="C10" s="48" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>649</v>
-      </c>
-      <c r="B8" s="47" t="s">
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="55" t="s">
+        <v>668</v>
+      </c>
+      <c r="B12" s="55" t="s">
+        <v>670</v>
+      </c>
+      <c r="C12" s="55" t="s">
         <v>780</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="D12" s="55" t="s">
+        <v>683</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>687</v>
+      </c>
+      <c r="F12" s="55" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="47" t="s">
-        <v>653</v>
-      </c>
-      <c r="B9" s="47" t="s">
+      <c r="G12" s="55" t="s">
         <v>782</v>
       </c>
-      <c r="C9" s="47" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="B10" s="47" t="s">
+      <c r="H12" s="55" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="56" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="57" t="s">
         <v>783</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C13" s="57" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="47" t="s">
-        <v>659</v>
-      </c>
-      <c r="B11" s="47" t="s">
+      <c r="D13" s="58" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E13" s="57" t="s">
         <v>785</v>
       </c>
-      <c r="C11" s="47" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="47" t="s">
-        <v>661</v>
-      </c>
-      <c r="B12" s="47" t="s">
+      <c r="F13" s="57" t="s">
         <v>786</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="G13" s="57" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="s">
-        <v>664</v>
-      </c>
-      <c r="B13" s="47" t="s">
+      <c r="H13" s="59" t="n">
+        <v>46541</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="57" t="s">
         <v>788</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C14" s="57" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="44" t="s">
+      <c r="D14" s="58" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E14" s="57" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="s">
-        <v>668</v>
-      </c>
-      <c r="B16" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="C16" s="43" t="s">
-        <v>675</v>
-      </c>
-      <c r="D16" s="43" t="s">
-        <v>679</v>
-      </c>
-      <c r="E16" s="43" t="s">
-        <v>683</v>
-      </c>
-      <c r="F16" s="43" t="s">
-        <v>687</v>
-      </c>
-      <c r="G16" s="43" t="s">
-        <v>357</v>
-      </c>
-      <c r="H16" s="43" t="s">
+      <c r="F14" s="57" t="s">
         <v>791</v>
       </c>
-      <c r="I16" s="43" t="s">
-        <v>694</v>
-      </c>
-      <c r="J16" s="43" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="47" t="s">
+      <c r="G14" s="57" t="s">
         <v>792</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="H14" s="59" t="n">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="57" t="s">
         <v>793</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="C15" s="57" t="s">
         <v>794</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="D15" s="58" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E15" s="57" t="s">
         <v>795</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="F15" s="57" t="s">
         <v>796</v>
       </c>
-      <c r="G17" s="47" t="s">
+      <c r="G15" s="57" t="s">
         <v>797</v>
       </c>
-      <c r="H17" s="47" t="s">
+      <c r="H15" s="59" t="n">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="57" t="s">
         <v>798</v>
       </c>
-      <c r="I17" s="47" t="s">
+      <c r="C16" s="57" t="s">
         <v>799</v>
       </c>
-      <c r="J17" s="47" t="s">
+      <c r="D16" s="58" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E16" s="57" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" s="47" t="s">
+      <c r="F16" s="57" t="s">
         <v>801</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="G16" s="57" t="s">
         <v>802</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="H16" s="59" t="n">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="57" t="s">
         <v>803</v>
       </c>
-      <c r="E18" s="47" t="s">
+      <c r="C17" s="57" t="s">
         <v>804</v>
       </c>
-      <c r="F18" s="47" t="s">
+      <c r="D17" s="58" t="n">
+        <v>250000</v>
+      </c>
+      <c r="E17" s="57" t="s">
+        <v>790</v>
+      </c>
+      <c r="F17" s="57" t="s">
         <v>805</v>
       </c>
-      <c r="G18" s="47" t="s">
+      <c r="G17" s="57" t="s">
         <v>806</v>
       </c>
-      <c r="H18" s="47" t="s">
+      <c r="H17" s="59" t="n">
+        <v>46321</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="60" t="s">
+        <v>610</v>
+      </c>
+      <c r="D18" s="61" t="n">
+        <f aca="false">SUM(D13:D17)</f>
+        <v>397500</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="62" t="s">
         <v>807</v>
       </c>
-      <c r="I18" s="47" t="s">
+      <c r="B20" s="62"/>
+      <c r="C20" s="62"/>
+      <c r="D20" s="62"/>
+      <c r="E20" s="62"/>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+    </row>
+    <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="63" t="s">
         <v>808</v>
       </c>
-      <c r="J18" s="47" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="n">
-        <v>3</v>
-      </c>
-      <c r="B19" s="47" t="s">
+      <c r="B21" s="63"/>
+      <c r="C21" s="63"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="64" t="s">
         <v>809</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="64"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="65" t="s">
         <v>810</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="B23" s="65"/>
+      <c r="C23" s="65"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
+      <c r="H23" s="65"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="65" t="s">
         <v>811</v>
       </c>
-      <c r="E19" s="47" t="s">
+      <c r="B24" s="65"/>
+      <c r="C24" s="65"/>
+      <c r="D24" s="65"/>
+      <c r="E24" s="65"/>
+      <c r="F24" s="65"/>
+      <c r="G24" s="65"/>
+      <c r="H24" s="65"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="65" t="s">
         <v>812</v>
       </c>
-      <c r="F19" s="47" t="s">
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="65" t="s">
         <v>813</v>
       </c>
-      <c r="G19" s="47" t="s">
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="65" t="s">
         <v>814</v>
       </c>
-      <c r="H19" s="47" t="s">
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
+      <c r="D27" s="65"/>
+      <c r="E27" s="65"/>
+      <c r="F27" s="65"/>
+      <c r="G27" s="65"/>
+      <c r="H27" s="65"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="66" t="s">
         <v>815</v>
       </c>
-      <c r="I19" s="47" t="s">
-        <v>816</v>
-      </c>
-      <c r="J19" s="47" t="s">
-        <v>777</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="47" t="n">
-        <v>4</v>
-      </c>
-      <c r="B20" s="47" t="s">
-        <v>817</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>793</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>818</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>819</v>
-      </c>
-      <c r="F20" s="47" t="s">
-        <v>820</v>
-      </c>
-      <c r="G20" s="47" t="s">
-        <v>821</v>
-      </c>
-      <c r="H20" s="47" t="s">
-        <v>822</v>
-      </c>
-      <c r="I20" s="47" t="s">
-        <v>823</v>
-      </c>
-      <c r="J20" s="47" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="B21" s="47" t="s">
-        <v>825</v>
-      </c>
-      <c r="C21" s="47" t="s">
-        <v>826</v>
-      </c>
-      <c r="D21" s="47" t="s">
-        <v>827</v>
-      </c>
-      <c r="E21" s="47" t="s">
-        <v>828</v>
-      </c>
-      <c r="F21" s="47" t="s">
-        <v>805</v>
-      </c>
-      <c r="G21" s="47" t="s">
-        <v>829</v>
-      </c>
-      <c r="H21" s="47" t="s">
-        <v>830</v>
-      </c>
-      <c r="I21" s="47" t="s">
-        <v>831</v>
-      </c>
-      <c r="J21" s="47" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="s">
-        <v>774</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>832</v>
-      </c>
-      <c r="C22" s="50" t="s">
-        <v>676</v>
-      </c>
-      <c r="D22" s="50" t="s">
-        <v>833</v>
-      </c>
-      <c r="E22" s="50" t="s">
-        <v>684</v>
-      </c>
-      <c r="F22" s="50" t="s">
-        <v>688</v>
-      </c>
-      <c r="G22" s="50" t="s">
-        <v>834</v>
-      </c>
-      <c r="H22" s="50" t="s">
-        <v>835</v>
-      </c>
-      <c r="I22" s="50" t="s">
-        <v>836</v>
-      </c>
-      <c r="J22" s="50" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D24" s="51" t="s">
-        <v>838</v>
-      </c>
-      <c r="E24" s="52" t="n">
-        <f aca="false">SUMPRODUCT(VALUE(SUBSTITUTE(E17:E21,",","")))</f>
-        <v>397500</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="44" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="43" t="s">
-        <v>748</v>
-      </c>
-      <c r="C28" s="43" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="47" t="s">
-        <v>750</v>
-      </c>
-      <c r="C29" s="47" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="135.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="47" t="s">
-        <v>752</v>
-      </c>
-      <c r="C30" s="47" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="47" t="s">
-        <v>754</v>
-      </c>
-      <c r="C31" s="47" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="47" t="s">
-        <v>756</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="47" t="s">
-        <v>758</v>
-      </c>
-      <c r="C33" s="47" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="47" t="s">
-        <v>760</v>
-      </c>
-      <c r="C34" s="47" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="47" t="s">
-        <v>762</v>
-      </c>
-      <c r="C35" s="47" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="47" t="s">
-        <v>764</v>
-      </c>
-      <c r="C36" s="47" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="47" t="s">
-        <v>766</v>
-      </c>
-      <c r="C37" s="47" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="47" t="s">
-        <v>768</v>
-      </c>
-      <c r="C38" s="47" t="s">
-        <v>769</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A27:H27"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6314,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>839</v>
+        <v>816</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>628</v>
@@ -6334,17 +6859,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>841</v>
+        <v>818</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>843</v>
+        <v>820</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>13</v>
@@ -6355,17 +6880,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>844</v>
+        <v>821</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>845</v>
+        <v>822</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>13</v>
@@ -6376,19 +6901,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>846</v>
+        <v>823</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>849</v>
+        <v>826</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>648</v>
@@ -6399,17 +6924,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>357</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>13</v>
@@ -6420,17 +6945,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>472</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>13</v>
@@ -6441,17 +6966,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>352</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>13</v>
@@ -6462,19 +6987,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>477</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>852</v>
+        <v>829</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>853</v>
+        <v>830</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>854</v>
+        <v>831</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -6483,19 +7008,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>855</v>
+        <v>832</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>856</v>
+        <v>833</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>708</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -6504,19 +7029,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>648</v>
@@ -6527,19 +7052,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>863</v>
+        <v>840</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>865</v>
+        <v>842</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -6548,19 +7073,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>866</v>
+        <v>843</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>867</v>
+        <v>844</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>868</v>
+        <v>845</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -6569,19 +7094,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>870</v>
+        <v>847</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>871</v>
+        <v>848</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>689</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>872</v>
+        <v>849</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>648</v>
@@ -6592,19 +7117,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>697</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>873</v>
+        <v>850</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>685</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>874</v>
+        <v>851</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>648</v>
@@ -6615,19 +7140,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>875</v>
+        <v>852</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>876</v>
+        <v>853</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>877</v>
+        <v>854</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>878</v>
+        <v>855</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -6636,19 +7161,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>879</v>
+        <v>856</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>880</v>
+        <v>857</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>881</v>
+        <v>858</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -6657,19 +7182,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>882</v>
+        <v>859</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>883</v>
+        <v>860</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>884</v>
+        <v>861</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -6678,19 +7203,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>885</v>
+        <v>862</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>886</v>
+        <v>863</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>877</v>
+        <v>854</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>887</v>
+        <v>864</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -6699,19 +7224,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>869</v>
+        <v>846</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>888</v>
+        <v>865</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>889</v>
+        <v>866</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>877</v>
+        <v>854</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>890</v>
+        <v>867</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -6720,19 +7245,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>891</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>892</v>
-      </c>
       <c r="E20" s="4" t="s">
-        <v>853</v>
+        <v>830</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>893</v>
+        <v>870</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -6741,17 +7266,17 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>895</v>
+        <v>872</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>897</v>
+        <v>874</v>
       </c>
       <c r="G21" s="4" t="s">
         <v>648</v>
@@ -6762,17 +7287,17 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>664</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -6784,12 +7309,12 @@
         <v>619</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>900</v>
+        <v>877</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4" t="s">
-        <v>901</v>
+        <v>878</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -6801,12 +7326,12 @@
         <v>619</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="G24" s="4"/>
     </row>
@@ -6818,12 +7343,12 @@
         <v>619</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>904</v>
+        <v>881</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4" t="s">
-        <v>905</v>
+        <v>882</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -6835,12 +7360,12 @@
         <v>619</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -6862,13 +7387,13 @@
     </row>
     <row r="31" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="46" t="s">
-        <v>907</v>
+        <v>884</v>
       </c>
       <c r="C31" s="46" t="s">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="D31" s="46" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6890,18 +7415,18 @@
         <v>685</v>
       </c>
       <c r="D33" s="46" t="s">
-        <v>910</v>
+        <v>887</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="46" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="C34" s="46" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>913</v>
+        <v>890</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6909,10 +7434,10 @@
         <v>741</v>
       </c>
       <c r="C35" s="46" t="s">
-        <v>914</v>
+        <v>891</v>
       </c>
       <c r="D35" s="46" t="s">
-        <v>915</v>
+        <v>892</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6923,7 +7448,7 @@
         <v>745</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -6942,369 +7467,415 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.27"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="53" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="67" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="70" t="s">
+        <v>477</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>895</v>
+      </c>
+      <c r="G1" s="69"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="72" t="s">
+        <v>821</v>
+      </c>
+      <c r="B2" s="73" t="s">
+        <v>896</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="70" t="s">
+        <v>832</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>897</v>
+      </c>
+      <c r="G2" s="74"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="72" t="s">
+        <v>823</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>898</v>
+      </c>
+      <c r="C3" s="73"/>
+      <c r="D3" s="74"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="74"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>899</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="70" t="s">
+        <v>835</v>
+      </c>
+      <c r="F4" s="71" t="n">
+        <v>1002</v>
+      </c>
+      <c r="G4" s="74"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="72" t="s">
+        <v>472</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>900</v>
+      </c>
+      <c r="C5" s="73"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="70" t="s">
+        <v>839</v>
+      </c>
+      <c r="F5" s="75" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G5" s="74"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>901</v>
+      </c>
+      <c r="E6" s="77" t="s">
+        <v>902</v>
+      </c>
+      <c r="F6" s="0" t="n">
+        <f aca="false">COUNTA(A8:A15)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="78" t="s">
+        <v>847</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>697</v>
+      </c>
+      <c r="C7" s="78" t="s">
+        <v>357</v>
+      </c>
+      <c r="D7" s="78" t="s">
+        <v>472</v>
+      </c>
+      <c r="E7" s="78" t="s">
+        <v>352</v>
+      </c>
+      <c r="F7" s="78" t="s">
+        <v>862</v>
+      </c>
+      <c r="G7" s="78" t="s">
+        <v>865</v>
+      </c>
+      <c r="H7" s="78" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="79" t="s">
+        <v>903</v>
+      </c>
+      <c r="B8" s="80" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C8" s="79" t="s">
+        <v>904</v>
+      </c>
+      <c r="D8" s="79" t="s">
+        <v>905</v>
+      </c>
+      <c r="E8" s="79" t="s">
+        <v>906</v>
+      </c>
+      <c r="F8" s="79" t="s">
+        <v>907</v>
+      </c>
+      <c r="G8" s="81" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H8" s="82" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="83" t="s">
+        <v>908</v>
+      </c>
+      <c r="B9" s="84" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C9" s="83" t="s">
+        <v>909</v>
+      </c>
+      <c r="D9" s="83" t="s">
+        <v>910</v>
+      </c>
+      <c r="E9" s="83" t="s">
+        <v>911</v>
+      </c>
+      <c r="F9" s="83" t="s">
+        <v>912</v>
+      </c>
+      <c r="G9" s="85" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H9" s="86" t="n">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="83" t="s">
+        <v>913</v>
+      </c>
+      <c r="B10" s="84" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C10" s="83" t="s">
+        <v>914</v>
+      </c>
+      <c r="D10" s="83" t="s">
+        <v>915</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>916</v>
+      </c>
+      <c r="F10" s="83" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="54" t="s">
+      <c r="G10" s="85" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H10" s="86" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="83" t="s">
+        <v>903</v>
+      </c>
+      <c r="B11" s="84" t="n">
+        <v>46251</v>
+      </c>
+      <c r="C11" s="83" t="s">
         <v>918</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
-        <v>841</v>
-      </c>
-      <c r="B4" s="47" t="s">
+      <c r="D11" s="83" t="s">
         <v>919</v>
       </c>
-      <c r="D4" s="43" t="s">
-        <v>477</v>
-      </c>
-      <c r="E4" s="47" t="s">
+      <c r="E11" s="83" t="s">
         <v>920</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
-        <v>844</v>
-      </c>
-      <c r="B5" s="47" t="s">
+      <c r="F11" s="83" t="s">
         <v>921</v>
       </c>
-      <c r="D5" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="E5" s="47" t="s">
+      <c r="G11" s="85" t="n">
+        <v>46251</v>
+      </c>
+      <c r="H11" s="86" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="83" t="s">
+        <v>903</v>
+      </c>
+      <c r="B12" s="84" t="n">
+        <v>46250</v>
+      </c>
+      <c r="C12" s="83" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
-        <v>846</v>
-      </c>
-      <c r="B6" s="47" t="s">
+      <c r="D12" s="83" t="s">
         <v>923</v>
       </c>
-      <c r="D6" s="43" t="s">
-        <v>858</v>
-      </c>
-      <c r="E6" s="47" t="n">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
-        <v>357</v>
-      </c>
-      <c r="B7" s="47" t="s">
+      <c r="E12" s="83" t="s">
         <v>924</v>
       </c>
-      <c r="D7" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="E7" s="55" t="n">
-        <v>46255</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>472</v>
-      </c>
-      <c r="B8" s="47" t="s">
+      <c r="F12" s="83" t="s">
         <v>925</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
-        <v>352</v>
-      </c>
-      <c r="B9" s="47" t="s">
+      <c r="G12" s="85" t="n">
+        <v>46250</v>
+      </c>
+      <c r="H12" s="86" t="n">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="83" t="s">
+        <v>903</v>
+      </c>
+      <c r="B13" s="84" t="n">
+        <v>46254</v>
+      </c>
+      <c r="C13" s="83" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="43" t="s">
-        <v>866</v>
-      </c>
-      <c r="E10" s="47" t="n">
-        <f aca="false">COUNTA(A13:A20)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="s">
-        <v>870</v>
-      </c>
-      <c r="B12" s="43" t="s">
-        <v>697</v>
-      </c>
-      <c r="C12" s="43" t="s">
-        <v>357</v>
-      </c>
-      <c r="D12" s="43" t="s">
-        <v>472</v>
-      </c>
-      <c r="E12" s="43" t="s">
-        <v>352</v>
-      </c>
-      <c r="F12" s="43" t="s">
-        <v>885</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>888</v>
-      </c>
-      <c r="H12" s="43" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="s">
+      <c r="D13" s="83" t="s">
+        <v>905</v>
+      </c>
+      <c r="E13" s="83" t="s">
         <v>927</v>
       </c>
-      <c r="B13" s="55" t="n">
+      <c r="F13" s="83" t="s">
+        <v>928</v>
+      </c>
+      <c r="G13" s="85" t="n">
         <v>46254</v>
       </c>
-      <c r="C13" s="47" t="s">
-        <v>797</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>928</v>
-      </c>
-      <c r="E13" s="47" t="s">
-        <v>798</v>
-      </c>
-      <c r="F13" s="47" t="s">
+      <c r="H13" s="86" t="n">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="83" t="s">
+        <v>903</v>
+      </c>
+      <c r="B14" s="84" t="n">
+        <v>46253</v>
+      </c>
+      <c r="C14" s="83" t="s">
         <v>929</v>
       </c>
-      <c r="G13" s="55" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H13" s="56" t="n">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="47" t="s">
+      <c r="D14" s="83" t="s">
         <v>930</v>
       </c>
-      <c r="B14" s="55" t="n">
+      <c r="E14" s="83" t="s">
+        <v>931</v>
+      </c>
+      <c r="F14" s="83" t="s">
+        <v>932</v>
+      </c>
+      <c r="G14" s="85" t="n">
         <v>46253</v>
       </c>
-      <c r="C14" s="47" t="s">
-        <v>806</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>931</v>
-      </c>
-      <c r="E14" s="47" t="s">
-        <v>807</v>
-      </c>
-      <c r="F14" s="47" t="s">
-        <v>932</v>
-      </c>
-      <c r="G14" s="55" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H14" s="56" t="n">
-        <v>45000</v>
+      <c r="H14" s="86" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="83" t="s">
+        <v>903</v>
+      </c>
+      <c r="B15" s="84" t="n">
+        <v>46252</v>
+      </c>
+      <c r="C15" s="83" t="s">
         <v>933</v>
       </c>
-      <c r="B15" s="55" t="n">
+      <c r="D15" s="83" t="s">
+        <v>934</v>
+      </c>
+      <c r="E15" s="83" t="s">
+        <v>935</v>
+      </c>
+      <c r="F15" s="83" t="s">
+        <v>936</v>
+      </c>
+      <c r="G15" s="85" t="n">
         <v>46252</v>
       </c>
-      <c r="C15" s="47" t="s">
-        <v>821</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>934</v>
-      </c>
-      <c r="E15" s="47" t="s">
-        <v>935</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>936</v>
-      </c>
-      <c r="G15" s="55" t="n">
-        <v>46252</v>
-      </c>
-      <c r="H15" s="56" t="n">
-        <v>100000</v>
+      <c r="H15" s="86" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="47" t="s">
-        <v>927</v>
-      </c>
-      <c r="B16" s="55" t="n">
-        <v>46251</v>
-      </c>
-      <c r="C16" s="47" t="s">
-        <v>814</v>
-      </c>
-      <c r="D16" s="47" t="s">
+      <c r="G16" s="0" t="s">
+        <v>610</v>
+      </c>
+      <c r="H16" s="87" t="n">
+        <f aca="false">SUM(H8:H15)</f>
+        <v>217500</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="76" t="s">
+        <v>664</v>
+      </c>
+      <c r="D18" s="88"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="89" t="s">
         <v>937</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="89"/>
+      <c r="F19" s="89"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="89"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="89"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>938</v>
       </c>
-      <c r="F16" s="47" t="s">
+      <c r="D28" s="0" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
         <v>939</v>
       </c>
-      <c r="G16" s="55" t="n">
-        <v>46251</v>
-      </c>
-      <c r="H16" s="56" t="n">
-        <v>7500</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="47" t="s">
-        <v>927</v>
-      </c>
-      <c r="B17" s="55" t="n">
-        <v>46250</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>829</v>
-      </c>
-      <c r="D17" s="47" t="s">
+      <c r="D29" s="0" t="s">
         <v>940</v>
       </c>
-      <c r="E17" s="47" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
         <v>941</v>
       </c>
-      <c r="F17" s="47" t="s">
+      <c r="D30" s="0" t="s">
         <v>942</v>
       </c>
-      <c r="G17" s="55" t="n">
-        <v>46250</v>
-      </c>
-      <c r="H17" s="56" t="n">
-        <v>22000</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
-        <v>927</v>
-      </c>
-      <c r="B18" s="55" t="n">
-        <v>46254</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>943</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>928</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>944</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>945</v>
-      </c>
-      <c r="G18" s="55" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H18" s="56" t="n">
-        <v>3500</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="s">
-        <v>927</v>
-      </c>
-      <c r="B19" s="55" t="n">
-        <v>46253</v>
-      </c>
-      <c r="C19" s="47" t="s">
-        <v>946</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>947</v>
-      </c>
-      <c r="E19" s="47" t="s">
-        <v>948</v>
-      </c>
-      <c r="F19" s="47" t="s">
-        <v>949</v>
-      </c>
-      <c r="G19" s="55" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H19" s="56" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="47" t="s">
-        <v>927</v>
-      </c>
-      <c r="B20" s="55" t="n">
-        <v>46252</v>
-      </c>
-      <c r="C20" s="47" t="s">
-        <v>950</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>951</v>
-      </c>
-      <c r="E20" s="47" t="s">
-        <v>952</v>
-      </c>
-      <c r="F20" s="47" t="s">
-        <v>953</v>
-      </c>
-      <c r="G20" s="55" t="n">
-        <v>46252</v>
-      </c>
-      <c r="H20" s="56" t="n">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G21" s="57" t="s">
-        <v>610</v>
-      </c>
-      <c r="H21" s="58" t="n">
-        <f aca="false">SUM(H13:H20)</f>
-        <v>217500</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="43" t="s">
-        <v>664</v>
-      </c>
-      <c r="B23" s="47" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>955</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>956</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A19:F21"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -7339,7 +7910,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="D1" s="43" t="s">
         <v>628</v>
@@ -7359,17 +7930,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>841</v>
+        <v>818</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>843</v>
+        <v>820</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>13</v>
@@ -7380,17 +7951,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>844</v>
+        <v>821</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>845</v>
+        <v>822</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>13</v>
@@ -7401,19 +7972,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>846</v>
+        <v>823</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>848</v>
+        <v>825</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>849</v>
+        <v>826</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>648</v>
@@ -7424,17 +7995,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>357</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>13</v>
@@ -7445,17 +8016,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>472</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>13</v>
@@ -7466,17 +8037,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>840</v>
+        <v>817</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>352</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>842</v>
+        <v>819</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>850</v>
+        <v>827</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>13</v>
@@ -7487,19 +8058,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>477</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>852</v>
+        <v>829</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>853</v>
+        <v>830</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>854</v>
+        <v>831</v>
       </c>
       <c r="G8" s="4"/>
     </row>
@@ -7508,19 +8079,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>855</v>
+        <v>832</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>856</v>
+        <v>833</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>708</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>857</v>
+        <v>834</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -7529,19 +8100,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>858</v>
+        <v>835</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>859</v>
+        <v>836</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>860</v>
+        <v>837</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>861</v>
+        <v>838</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>648</v>
@@ -7552,19 +8123,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>851</v>
+        <v>828</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>862</v>
+        <v>839</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>863</v>
+        <v>840</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>865</v>
+        <v>842</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -7573,17 +8144,17 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>959</v>
+        <v>945</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>960</v>
+        <v>946</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4" t="s">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -7592,19 +8163,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>962</v>
+        <v>948</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>963</v>
+        <v>949</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>648</v>
@@ -7615,19 +8186,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>965</v>
+        <v>951</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>864</v>
+        <v>841</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>967</v>
+        <v>953</v>
       </c>
       <c r="G14" s="4"/>
     </row>
@@ -7636,17 +8207,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>891</v>
+        <v>868</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>968</v>
+        <v>954</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4" t="s">
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -7655,7 +8226,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>114</v>
@@ -7663,7 +8234,7 @@
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4" t="s">
-        <v>970</v>
+        <v>956</v>
       </c>
       <c r="G16" s="4"/>
     </row>
@@ -7672,17 +8243,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>610</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>896</v>
+        <v>873</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
-        <v>971</v>
+        <v>957</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -7691,17 +8262,17 @@
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>894</v>
+        <v>871</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>664</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>898</v>
+        <v>875</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
-        <v>899</v>
+        <v>876</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -7713,12 +8284,12 @@
         <v>619</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>900</v>
+        <v>877</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
-        <v>905</v>
+        <v>882</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -7730,12 +8301,12 @@
         <v>619</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>902</v>
+        <v>879</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -7747,12 +8318,12 @@
         <v>619</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>904</v>
+        <v>881</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4" t="s">
-        <v>905</v>
+        <v>882</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -7764,12 +8335,12 @@
         <v>619</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>906</v>
+        <v>883</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4" t="s">
-        <v>903</v>
+        <v>880</v>
       </c>
       <c r="G22" s="4"/>
     </row>
@@ -7791,13 +8362,13 @@
     </row>
     <row r="27" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="46" t="s">
-        <v>907</v>
+        <v>884</v>
       </c>
       <c r="C27" s="46" t="s">
-        <v>908</v>
+        <v>885</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>909</v>
+        <v>886</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7819,18 +8390,18 @@
         <v>685</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>910</v>
+        <v>887</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="46" t="s">
-        <v>911</v>
+        <v>888</v>
       </c>
       <c r="C30" s="46" t="s">
-        <v>912</v>
+        <v>889</v>
       </c>
       <c r="D30" s="46" t="s">
-        <v>913</v>
+        <v>890</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7838,10 +8409,10 @@
         <v>741</v>
       </c>
       <c r="C31" s="46" t="s">
-        <v>914</v>
+        <v>891</v>
       </c>
       <c r="D31" s="46" t="s">
-        <v>915</v>
+        <v>892</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7852,7 +8423,7 @@
         <v>745</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>916</v>
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -7871,301 +8442,367 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.27"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="53" t="s">
-        <v>972</v>
-      </c>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="67" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="70" t="s">
+        <v>477</v>
+      </c>
+      <c r="F1" s="71" t="s">
+        <v>895</v>
+      </c>
+      <c r="G1" s="69"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="54" t="s">
-        <v>973</v>
-      </c>
+      <c r="A2" s="72" t="s">
+        <v>821</v>
+      </c>
+      <c r="B2" s="73" t="s">
+        <v>896</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="70" t="s">
+        <v>832</v>
+      </c>
+      <c r="F2" s="71" t="s">
+        <v>897</v>
+      </c>
+      <c r="G2" s="74"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="72" t="s">
+        <v>823</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>898</v>
+      </c>
+      <c r="C3" s="73"/>
+      <c r="D3" s="74"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="74"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="43" t="s">
-        <v>841</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>919</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>477</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="43" t="s">
-        <v>844</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>921</v>
-      </c>
-      <c r="D5" s="43" t="s">
-        <v>855</v>
-      </c>
-      <c r="E5" s="47" t="s">
-        <v>922</v>
-      </c>
+      <c r="A4" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="B4" s="73" t="s">
+        <v>899</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="70" t="s">
+        <v>835</v>
+      </c>
+      <c r="F4" s="71" t="n">
+        <v>1001</v>
+      </c>
+      <c r="G4" s="74"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="72" t="s">
+        <v>472</v>
+      </c>
+      <c r="B5" s="73" t="s">
+        <v>900</v>
+      </c>
+      <c r="C5" s="73"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="70" t="s">
+        <v>839</v>
+      </c>
+      <c r="F5" s="75" t="n">
+        <v>46255</v>
+      </c>
+      <c r="G5" s="74"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
-        <v>846</v>
-      </c>
-      <c r="B6" s="47" t="s">
-        <v>923</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>858</v>
-      </c>
-      <c r="E6" s="47" t="n">
-        <v>1001</v>
+      <c r="A6" s="76" t="s">
+        <v>352</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="43" t="s">
-        <v>357</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>924</v>
-      </c>
-      <c r="D7" s="43" t="s">
-        <v>862</v>
-      </c>
-      <c r="E7" s="55" t="n">
-        <v>46255</v>
-      </c>
+      <c r="A7" s="78" t="s">
+        <v>945</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>948</v>
+      </c>
+      <c r="C7" s="78" t="s">
+        <v>951</v>
+      </c>
+      <c r="D7" s="78" t="s">
+        <v>868</v>
+      </c>
+      <c r="E7" s="90" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="90"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>472</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>925</v>
-      </c>
+      <c r="A8" s="91" t="s">
+        <v>720</v>
+      </c>
+      <c r="B8" s="91" t="n">
+        <v>500</v>
+      </c>
+      <c r="C8" s="92" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" s="93" t="n">
+        <f aca="false">B8*C8</f>
+        <v>12000</v>
+      </c>
+      <c r="E8" s="94"/>
+      <c r="F8" s="95"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="43" t="s">
-        <v>352</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>926</v>
-      </c>
+      <c r="A9" s="91" t="s">
+        <v>720</v>
+      </c>
+      <c r="B9" s="96" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" s="97" t="n">
+        <v>49</v>
+      </c>
+      <c r="D9" s="93" t="n">
+        <f aca="false">B9*C9</f>
+        <v>4900</v>
+      </c>
+      <c r="E9" s="98"/>
+      <c r="F9" s="99"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="91" t="s">
+        <v>720</v>
+      </c>
+      <c r="B10" s="96" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" s="97" t="n">
+        <v>36</v>
+      </c>
+      <c r="D10" s="93" t="n">
+        <f aca="false">B10*C10</f>
+        <v>1800</v>
+      </c>
+      <c r="E10" s="98"/>
+      <c r="F10" s="99"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="91" t="s">
+        <v>720</v>
+      </c>
+      <c r="B11" s="96" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" s="97" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="93" t="n">
+        <f aca="false">B11*C11</f>
+        <v>200</v>
+      </c>
+      <c r="E11" s="98"/>
+      <c r="F11" s="99"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="91" t="s">
+        <v>720</v>
+      </c>
+      <c r="B12" s="96" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="97" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="93" t="n">
+        <f aca="false">B12*C12</f>
+        <v>50</v>
+      </c>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="100" t="s">
+        <v>958</v>
+      </c>
+      <c r="B13" s="96" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" s="97" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="93" t="n">
+        <f aca="false">B13*C13</f>
+        <v>200</v>
+      </c>
+      <c r="E13" s="98"/>
+      <c r="F13" s="99"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="100" t="s">
+        <v>958</v>
+      </c>
+      <c r="B14" s="96" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" s="97" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="93" t="n">
+        <f aca="false">B14*C14</f>
+        <v>100</v>
+      </c>
+      <c r="E14" s="98"/>
+      <c r="F14" s="99"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="100" t="s">
+        <v>958</v>
+      </c>
+      <c r="B15" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="97" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="93" t="n">
+        <f aca="false">B15*C15</f>
+        <v>50</v>
+      </c>
+      <c r="E15" s="98"/>
+      <c r="F15" s="99"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="100" t="s">
+        <v>958</v>
+      </c>
+      <c r="B16" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="97" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" s="93" t="n">
+        <f aca="false">B16*C16</f>
+        <v>20</v>
+      </c>
+      <c r="E16" s="98"/>
+      <c r="F16" s="99"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="100" t="s">
+        <v>958</v>
+      </c>
+      <c r="B17" s="96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="97" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" s="101" t="n">
+        <f aca="false">B17*C17</f>
+        <v>10</v>
+      </c>
+      <c r="E17" s="98"/>
+      <c r="F17" s="99"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="102"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="102" t="s">
+        <v>610</v>
+      </c>
+      <c r="D18" s="103" t="n">
+        <f aca="false">SUM(D8:D17)</f>
+        <v>19330</v>
+      </c>
+      <c r="E18" s="104"/>
+      <c r="F18" s="105"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="76" t="s">
+        <v>664</v>
+      </c>
+      <c r="D19" s="88"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="89" t="s">
         <v>959</v>
       </c>
-      <c r="B11" s="43" t="s">
-        <v>962</v>
-      </c>
-      <c r="C11" s="43" t="s">
-        <v>965</v>
-      </c>
-      <c r="D11" s="43" t="s">
-        <v>891</v>
-      </c>
-      <c r="E11" s="43" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="47" t="s">
-        <v>720</v>
-      </c>
-      <c r="B12" s="47" t="n">
-        <v>500</v>
-      </c>
-      <c r="C12" s="47" t="n">
-        <v>24</v>
-      </c>
-      <c r="D12" s="59" t="n">
-        <f aca="false">B12*C12</f>
-        <v>12000</v>
-      </c>
-      <c r="E12" s="47"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="s">
-        <v>720</v>
-      </c>
-      <c r="B13" s="47" t="n">
-        <v>100</v>
-      </c>
-      <c r="C13" s="47" t="n">
-        <v>49</v>
-      </c>
-      <c r="D13" s="59" t="n">
-        <f aca="false">B13*C13</f>
-        <v>4900</v>
-      </c>
-      <c r="E13" s="47"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="47" t="s">
-        <v>720</v>
-      </c>
-      <c r="B14" s="47" t="n">
-        <v>50</v>
-      </c>
-      <c r="C14" s="47" t="n">
-        <v>36</v>
-      </c>
-      <c r="D14" s="59" t="n">
-        <f aca="false">B14*C14</f>
-        <v>1800</v>
-      </c>
-      <c r="E14" s="47"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="47" t="s">
-        <v>720</v>
-      </c>
-      <c r="B15" s="47" t="n">
-        <v>20</v>
-      </c>
-      <c r="C15" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D15" s="59" t="n">
-        <f aca="false">B15*C15</f>
-        <v>200</v>
-      </c>
-      <c r="E15" s="47"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="47" t="s">
-        <v>720</v>
-      </c>
-      <c r="B16" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="59" t="n">
-        <f aca="false">B16*C16</f>
-        <v>50</v>
-      </c>
-      <c r="E16" s="47"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="47" t="s">
-        <v>974</v>
-      </c>
-      <c r="B17" s="47" t="n">
-        <v>20</v>
-      </c>
-      <c r="C17" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" s="59" t="n">
-        <f aca="false">B17*C17</f>
-        <v>200</v>
-      </c>
-      <c r="E17" s="47"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="47" t="s">
-        <v>974</v>
-      </c>
-      <c r="B18" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="C18" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D18" s="59" t="n">
-        <f aca="false">B18*C18</f>
-        <v>100</v>
-      </c>
-      <c r="E18" s="47"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="47" t="s">
-        <v>974</v>
-      </c>
-      <c r="B19" s="47" t="n">
-        <v>5</v>
-      </c>
-      <c r="C19" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D19" s="59" t="n">
-        <f aca="false">B19*C19</f>
-        <v>50</v>
-      </c>
-      <c r="E19" s="47"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="47" t="s">
-        <v>974</v>
-      </c>
-      <c r="B20" s="47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D20" s="59" t="n">
-        <f aca="false">B20*C20</f>
-        <v>20</v>
-      </c>
-      <c r="E20" s="47"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="47" t="s">
-        <v>974</v>
-      </c>
-      <c r="B21" s="47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="47" t="n">
-        <v>10</v>
-      </c>
-      <c r="D21" s="59" t="n">
-        <f aca="false">B21*C21</f>
-        <v>10</v>
-      </c>
-      <c r="E21" s="47"/>
+      <c r="A21" s="89"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="89"/>
+      <c r="F21" s="89"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="57" t="s">
-        <v>610</v>
-      </c>
-      <c r="D22" s="60" t="n">
-        <f aca="false">SUM(D12:D21)</f>
-        <v>19330</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="82.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43" t="s">
-        <v>664</v>
-      </c>
-      <c r="B24" s="47" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>955</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>956</v>
+      <c r="A22" s="89"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="89"/>
+      <c r="F22" s="89"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
+        <v>938</v>
+      </c>
+      <c r="D28" s="0" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>939</v>
+      </c>
+      <c r="D29" s="0" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>941</v>
+      </c>
+      <c r="D30" s="0" t="s">
+        <v>942</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A20:F22"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8186,8 +8823,8 @@
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="61" t="s">
-        <v>976</v>
+      <c r="B2" s="106" t="s">
+        <v>960</v>
       </c>
     </row>
   </sheetData>
@@ -8228,7 +8865,7 @@
   <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="59.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="107" width="59.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
@@ -8240,39 +8877,39 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
-        <v>977</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="65" t="s">
-        <v>978</v>
-      </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="A1" s="108" t="s">
+        <v>961</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="110" t="s">
+        <v>962</v>
+      </c>
+      <c r="F1" s="110"/>
+      <c r="G1" s="110"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
     </row>
     <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67" t="s">
-        <v>979</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>980</v>
-      </c>
-      <c r="D2" s="68" t="s">
-        <v>981</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>982</v>
-      </c>
-      <c r="F2" s="69" t="s">
-        <v>983</v>
-      </c>
-      <c r="G2" s="70" t="s">
-        <v>984</v>
+      <c r="A2" s="111"/>
+      <c r="B2" s="112" t="s">
+        <v>963</v>
+      </c>
+      <c r="C2" s="113" t="s">
+        <v>964</v>
+      </c>
+      <c r="D2" s="113" t="s">
+        <v>965</v>
+      </c>
+      <c r="E2" s="114" t="s">
+        <v>966</v>
+      </c>
+      <c r="F2" s="114" t="s">
+        <v>967</v>
+      </c>
+      <c r="G2" s="115" t="s">
+        <v>968</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>5</v>
@@ -8282,10 +8919,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="66" t="s">
-        <v>985</v>
-      </c>
-      <c r="B3" s="67"/>
+      <c r="A3" s="111" t="s">
+        <v>969</v>
+      </c>
+      <c r="B3" s="112"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -8294,141 +8931,141 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71" t="s">
-        <v>986</v>
-      </c>
-      <c r="B4" s="72"/>
+      <c r="A4" s="116" t="s">
+        <v>970</v>
+      </c>
+      <c r="B4" s="117"/>
       <c r="C4" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="s">
-        <v>991</v>
-      </c>
-      <c r="B5" s="72"/>
+      <c r="A5" s="116" t="s">
+        <v>975</v>
+      </c>
+      <c r="B5" s="117"/>
       <c r="C5" s="4" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="s">
-        <v>995</v>
-      </c>
-      <c r="B6" s="72"/>
+      <c r="A6" s="116" t="s">
+        <v>979</v>
+      </c>
+      <c r="B6" s="117"/>
       <c r="C6" s="4" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="s">
-        <v>999</v>
-      </c>
-      <c r="B7" s="72"/>
+      <c r="A7" s="116" t="s">
+        <v>983</v>
+      </c>
+      <c r="B7" s="117"/>
       <c r="C7" s="4" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B8" s="72"/>
+      <c r="A8" s="116" t="s">
+        <v>987</v>
+      </c>
+      <c r="B8" s="117"/>
       <c r="C8" s="4" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B9" s="72"/>
+      <c r="A9" s="116" t="s">
+        <v>991</v>
+      </c>
+      <c r="B9" s="117"/>
       <c r="C9" s="4" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B10" s="72"/>
+      <c r="A10" s="116" t="s">
+        <v>995</v>
+      </c>
+      <c r="B10" s="117"/>
       <c r="C10" s="4" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>290</v>
@@ -8437,23 +9074,23 @@
         <v>307</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B11" s="72"/>
+      <c r="A11" s="116" t="s">
+        <v>999</v>
+      </c>
+      <c r="B11" s="117"/>
       <c r="C11" s="4" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>290</v>
@@ -8462,23 +9099,23 @@
         <v>307</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B12" s="72"/>
+      <c r="A12" s="116" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B12" s="117"/>
       <c r="C12" s="4" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1021</v>
+        <v>1005</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>290</v>
@@ -8487,256 +9124,256 @@
         <v>307</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B13" s="72"/>
+      <c r="A13" s="116" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B13" s="117"/>
       <c r="C13" s="4" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B14" s="72"/>
+      <c r="A14" s="116" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B14" s="117"/>
       <c r="C14" s="4" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1029</v>
+        <v>1013</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B15" s="72"/>
+      <c r="A15" s="116" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B15" s="117"/>
       <c r="C15" s="4" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="73" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B16" s="72"/>
+      <c r="A16" s="118" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B16" s="117"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>1036</v>
+        <v>1020</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="71" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B17" s="72"/>
+      <c r="A17" s="116" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B17" s="117"/>
       <c r="C17" s="4" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4" t="s">
         <v>111</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="71" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B18" s="72"/>
+      <c r="A18" s="116" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B18" s="117"/>
       <c r="C18" s="4" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1043</v>
+        <v>1027</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="73" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B19" s="72"/>
+      <c r="A19" s="118" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B19" s="117"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>1046</v>
+        <v>1030</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="74" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B20" s="72"/>
+      <c r="A20" s="119" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B20" s="117"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B21" s="67"/>
+      <c r="A21" s="116" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B21" s="112"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="71" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B22" s="67"/>
+      <c r="A22" s="116" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B22" s="112"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1054</v>
+        <v>1038</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B23" s="67"/>
+      <c r="A23" s="116" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B23" s="112"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>1057</v>
+        <v>1041</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B24" s="67"/>
+      <c r="A24" s="116" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B24" s="112"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1060</v>
+        <v>1044</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="74" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B25" s="75"/>
+      <c r="A25" s="119" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B25" s="120"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="76"/>
+      <c r="A26" s="121"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
       <c r="E26" s="17"/>
@@ -8769,7 +9406,7 @@
   <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="59.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="107" width="59.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="69.29"/>
@@ -8781,37 +9418,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
-        <v>977</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="A1" s="108" t="s">
+        <v>961</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
     </row>
     <row r="2" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67" t="s">
-        <v>979</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>980</v>
-      </c>
-      <c r="D2" s="68" t="s">
-        <v>981</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>982</v>
-      </c>
-      <c r="F2" s="69" t="s">
-        <v>983</v>
-      </c>
-      <c r="G2" s="70" t="s">
-        <v>984</v>
+      <c r="A2" s="111"/>
+      <c r="B2" s="112" t="s">
+        <v>963</v>
+      </c>
+      <c r="C2" s="113" t="s">
+        <v>964</v>
+      </c>
+      <c r="D2" s="113" t="s">
+        <v>965</v>
+      </c>
+      <c r="E2" s="114" t="s">
+        <v>966</v>
+      </c>
+      <c r="F2" s="114" t="s">
+        <v>967</v>
+      </c>
+      <c r="G2" s="115" t="s">
+        <v>968</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>5</v>
@@ -8821,10 +9458,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="66" t="s">
-        <v>985</v>
-      </c>
-      <c r="B3" s="67"/>
+      <c r="A3" s="111" t="s">
+        <v>969</v>
+      </c>
+      <c r="B3" s="112"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -8834,141 +9471,141 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71" t="s">
-        <v>986</v>
-      </c>
-      <c r="B4" s="72"/>
+      <c r="A4" s="116" t="s">
+        <v>970</v>
+      </c>
+      <c r="B4" s="117"/>
       <c r="C4" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B5" s="72"/>
+      <c r="A5" s="116" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B5" s="117"/>
       <c r="C5" s="4" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B6" s="72"/>
+      <c r="A6" s="116" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B6" s="117"/>
       <c r="C6" s="4" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B7" s="72"/>
+      <c r="A7" s="116" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B7" s="117"/>
       <c r="C7" s="4" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B8" s="72"/>
+      <c r="A8" s="116" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B8" s="117"/>
       <c r="C8" s="4" t="s">
-        <v>1067</v>
+        <v>1051</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1068</v>
+        <v>1052</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>1069</v>
+        <v>1053</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B9" s="72"/>
+      <c r="A9" s="116" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B9" s="117"/>
       <c r="C9" s="4" t="s">
-        <v>1071</v>
+        <v>1055</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1072</v>
+        <v>1056</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>1073</v>
+        <v>1057</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="s">
-        <v>1074</v>
-      </c>
-      <c r="B10" s="72"/>
+      <c r="A10" s="116" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B10" s="117"/>
       <c r="C10" s="4" t="s">
-        <v>1075</v>
+        <v>1059</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1074</v>
+        <v>1058</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>290</v>
@@ -8977,65 +9614,65 @@
         <v>307</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B11" s="72"/>
+      <c r="A11" s="116" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B11" s="117"/>
       <c r="C11" s="4" t="s">
-        <v>1077</v>
+        <v>1061</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1078</v>
-      </c>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
+        <v>1062</v>
+      </c>
+      <c r="E11" s="122"/>
+      <c r="F11" s="123"/>
       <c r="G11" s="4" t="s">
-        <v>1079</v>
+        <v>1063</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B12" s="72"/>
+      <c r="A12" s="116" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B12" s="117"/>
       <c r="C12" s="4" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B13" s="72"/>
+      <c r="A13" s="116" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B13" s="117"/>
       <c r="C13" s="4" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1081</v>
+        <v>1065</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>290</v>
@@ -9044,400 +9681,400 @@
         <v>307</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B14" s="72"/>
+      <c r="A14" s="116" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B14" s="117"/>
       <c r="C14" s="4" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1082</v>
+        <v>1066</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B15" s="72"/>
+      <c r="A15" s="116" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B15" s="117"/>
       <c r="C15" s="4" t="s">
-        <v>1084</v>
+        <v>1068</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1085</v>
+        <v>1069</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="71" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B16" s="72"/>
+      <c r="A16" s="116" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B16" s="117"/>
       <c r="C16" s="4" t="s">
-        <v>1088</v>
+        <v>1072</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="71" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B17" s="72"/>
+      <c r="A17" s="116" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B17" s="117"/>
       <c r="C17" s="4" t="s">
-        <v>1092</v>
+        <v>1076</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1093</v>
+        <v>1077</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
-        <v>1094</v>
+        <v>1078</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="71" t="s">
-        <v>1095</v>
-      </c>
-      <c r="B18" s="72"/>
+      <c r="A18" s="116" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B18" s="117"/>
       <c r="C18" s="4" t="s">
-        <v>1096</v>
+        <v>1080</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1097</v>
+        <v>1081</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F18" s="4"/>
       <c r="G18" s="4" t="s">
-        <v>1098</v>
+        <v>1082</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B19" s="72"/>
+      <c r="A19" s="116" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B19" s="117"/>
       <c r="C19" s="4" t="s">
-        <v>1100</v>
+        <v>1084</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1101</v>
+        <v>1085</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="4" t="s">
-        <v>1102</v>
+        <v>1086</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="71" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B20" s="72"/>
+      <c r="A20" s="116" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B20" s="117"/>
       <c r="C20" s="4" t="s">
-        <v>1104</v>
+        <v>1088</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>1105</v>
+        <v>1089</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4" t="s">
-        <v>1106</v>
+        <v>1090</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B21" s="72"/>
+      <c r="A21" s="116" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B21" s="117"/>
       <c r="C21" s="4" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>1107</v>
+        <v>1091</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="73" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B22" s="72"/>
+      <c r="A22" s="118" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B22" s="117"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
       <c r="H22" s="4" t="s">
-        <v>1108</v>
+        <v>1092</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B23" s="72"/>
+      <c r="A23" s="116" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B23" s="117"/>
       <c r="C23" s="4" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="4" t="s">
         <v>111</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="73" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B24" s="72"/>
+      <c r="A24" s="118" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B24" s="117"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="5"/>
       <c r="H24" s="4" t="s">
-        <v>1109</v>
+        <v>1093</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="79" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B25" s="80"/>
+      <c r="A25" s="124" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B25" s="125"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="5"/>
       <c r="H25" s="4" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="81" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B26" s="82"/>
+      <c r="A26" s="126" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B26" s="127"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>1111</v>
+        <v>1095</v>
       </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="81" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B27" s="83"/>
+      <c r="A27" s="126" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B27" s="128"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
       <c r="H27" s="4" t="s">
-        <v>1112</v>
+        <v>1096</v>
       </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="81" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B28" s="82"/>
+      <c r="A28" s="126" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B28" s="127"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>1114</v>
+        <v>1098</v>
       </c>
       <c r="I28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="81" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B29" s="83"/>
+      <c r="A29" s="126" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B29" s="128"/>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4" t="s">
-        <v>1115</v>
+        <v>1099</v>
       </c>
       <c r="I29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="81" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B30" s="83"/>
+      <c r="A30" s="126" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B30" s="128"/>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="4" t="s">
-        <v>1117</v>
+        <v>1101</v>
       </c>
       <c r="I30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="81" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B31" s="83"/>
+      <c r="A31" s="126" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B31" s="128"/>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="4" t="s">
-        <v>1118</v>
+        <v>1102</v>
       </c>
       <c r="I31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="81" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B32" s="82"/>
+      <c r="A32" s="126" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B32" s="127"/>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="4" t="s">
-        <v>1120</v>
+        <v>1104</v>
       </c>
       <c r="I32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="81" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B33" s="83"/>
+      <c r="A33" s="126" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B33" s="128"/>
       <c r="C33" s="4"/>
       <c r="D33" s="4"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="4" t="s">
-        <v>1121</v>
+        <v>1105</v>
       </c>
       <c r="I33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="81" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B34" s="84"/>
+      <c r="A34" s="126" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B34" s="129"/>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="4" t="s">
-        <v>1122</v>
+        <v>1106</v>
       </c>
       <c r="I34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="76"/>
+      <c r="A35" s="121"/>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
     </row>
@@ -9469,7 +10106,7 @@
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="59.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="107" width="59.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="61.29"/>
@@ -9480,37 +10117,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
-        <v>977</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="A1" s="108" t="s">
+        <v>961</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
     </row>
     <row r="2" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67" t="s">
-        <v>979</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>980</v>
-      </c>
-      <c r="D2" s="68" t="s">
-        <v>981</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>982</v>
-      </c>
-      <c r="F2" s="69" t="s">
-        <v>983</v>
-      </c>
-      <c r="G2" s="70" t="s">
-        <v>984</v>
+      <c r="A2" s="111"/>
+      <c r="B2" s="112" t="s">
+        <v>963</v>
+      </c>
+      <c r="C2" s="113" t="s">
+        <v>964</v>
+      </c>
+      <c r="D2" s="113" t="s">
+        <v>965</v>
+      </c>
+      <c r="E2" s="114" t="s">
+        <v>966</v>
+      </c>
+      <c r="F2" s="114" t="s">
+        <v>967</v>
+      </c>
+      <c r="G2" s="115" t="s">
+        <v>968</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>5</v>
@@ -9520,10 +10157,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="66" t="s">
-        <v>985</v>
-      </c>
-      <c r="B3" s="67"/>
+      <c r="A3" s="111" t="s">
+        <v>969</v>
+      </c>
+      <c r="B3" s="112"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -9533,162 +10170,162 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71" t="s">
-        <v>986</v>
-      </c>
-      <c r="B4" s="72"/>
+      <c r="A4" s="116" t="s">
+        <v>970</v>
+      </c>
+      <c r="B4" s="117"/>
       <c r="C4" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B5" s="72"/>
+      <c r="A5" s="116" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B5" s="117"/>
       <c r="C5" s="4" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B6" s="72"/>
+      <c r="A6" s="116" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B6" s="117"/>
       <c r="C6" s="4" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B7" s="72"/>
+      <c r="A7" s="116" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B7" s="117"/>
       <c r="C7" s="4" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="s">
-        <v>1070</v>
-      </c>
-      <c r="B8" s="72"/>
+      <c r="A8" s="116" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B8" s="117"/>
       <c r="C8" s="4" t="s">
-        <v>1071</v>
+        <v>1055</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1072</v>
+        <v>1056</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>1073</v>
+        <v>1057</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
-        <v>1076</v>
-      </c>
-      <c r="B9" s="72"/>
+      <c r="A9" s="116" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B9" s="117"/>
       <c r="C9" s="4" t="s">
-        <v>1077</v>
+        <v>1061</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1078</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="78"/>
+        <v>1062</v>
+      </c>
+      <c r="E9" s="122"/>
+      <c r="F9" s="123"/>
       <c r="G9" s="4" t="s">
-        <v>1079</v>
+        <v>1063</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="s">
-        <v>1123</v>
-      </c>
-      <c r="B10" s="72"/>
+      <c r="A10" s="116" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B10" s="117"/>
       <c r="C10" s="4" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B11" s="72"/>
+      <c r="A11" s="116" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B11" s="117"/>
       <c r="C11" s="4" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1081</v>
+        <v>1065</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>290</v>
@@ -9697,306 +10334,306 @@
         <v>307</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B12" s="72"/>
+      <c r="A12" s="116" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B12" s="117"/>
       <c r="C12" s="4" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1082</v>
+        <v>1066</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F12" s="4"/>
       <c r="G12" s="4" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B13" s="72"/>
+      <c r="A13" s="116" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B13" s="117"/>
       <c r="C13" s="4" t="s">
-        <v>1084</v>
+        <v>1068</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1085</v>
+        <v>1069</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>1086</v>
+        <v>1070</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B14" s="72"/>
+      <c r="A14" s="116" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B14" s="117"/>
       <c r="C14" s="4" t="s">
-        <v>1088</v>
+        <v>1072</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1089</v>
+        <v>1073</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>1090</v>
+        <v>1074</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
-        <v>1091</v>
-      </c>
-      <c r="B15" s="72"/>
+      <c r="A15" s="116" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B15" s="117"/>
       <c r="C15" s="4" t="s">
-        <v>1092</v>
+        <v>1076</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1093</v>
+        <v>1077</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>1094</v>
+        <v>1078</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="71" t="s">
-        <v>1103</v>
-      </c>
-      <c r="B16" s="72"/>
+      <c r="A16" s="116" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B16" s="117"/>
       <c r="C16" s="4" t="s">
-        <v>1104</v>
+        <v>1088</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1105</v>
+        <v>1089</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>1106</v>
+        <v>1090</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="71" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B17" s="72"/>
+      <c r="A17" s="116" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B17" s="117"/>
       <c r="C17" s="4" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>1107</v>
+        <v>1091</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="73" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B18" s="72"/>
+      <c r="A18" s="118" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B18" s="117"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>1124</v>
+        <v>1108</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B19" s="72"/>
+      <c r="A19" s="116" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B19" s="117"/>
       <c r="C19" s="4" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
         <v>111</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="73" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B20" s="72"/>
+      <c r="A20" s="118" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B20" s="117"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>1126</v>
+        <v>1110</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="74" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B21" s="72"/>
+      <c r="A21" s="119" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B21" s="117"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="74" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B22" s="67"/>
+      <c r="A22" s="119" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B22" s="112"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="74" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B23" s="67"/>
+      <c r="A23" s="119" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B23" s="112"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>1054</v>
+        <v>1038</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="74" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B24" s="67"/>
+      <c r="A24" s="119" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B24" s="112"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1057</v>
+        <v>1041</v>
       </c>
       <c r="I24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B25" s="67"/>
+      <c r="A25" s="116" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B25" s="112"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>1060</v>
+        <v>1044</v>
       </c>
       <c r="I25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="74" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B26" s="75"/>
+      <c r="A26" s="119" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B26" s="120"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="I26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="76"/>
+      <c r="A27" s="121"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
-      <c r="E27" s="85"/>
-      <c r="F27" s="85"/>
+      <c r="E27" s="130"/>
+      <c r="F27" s="130"/>
       <c r="G27" s="17"/>
     </row>
   </sheetData>
@@ -11171,7 +11808,7 @@
   <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="62" width="59.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="107" width="59.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="57.42"/>
@@ -11183,37 +11820,37 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
-        <v>977</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="A1" s="108" t="s">
+        <v>961</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
     </row>
     <row r="2" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67" t="s">
-        <v>979</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>980</v>
-      </c>
-      <c r="D2" s="68" t="s">
-        <v>981</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>982</v>
-      </c>
-      <c r="F2" s="69" t="s">
-        <v>983</v>
-      </c>
-      <c r="G2" s="70" t="s">
-        <v>984</v>
+      <c r="A2" s="111"/>
+      <c r="B2" s="112" t="s">
+        <v>963</v>
+      </c>
+      <c r="C2" s="113" t="s">
+        <v>964</v>
+      </c>
+      <c r="D2" s="113" t="s">
+        <v>965</v>
+      </c>
+      <c r="E2" s="114" t="s">
+        <v>966</v>
+      </c>
+      <c r="F2" s="114" t="s">
+        <v>967</v>
+      </c>
+      <c r="G2" s="115" t="s">
+        <v>968</v>
       </c>
       <c r="H2" s="14" t="s">
         <v>5</v>
@@ -11223,10 +11860,10 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="66" t="s">
-        <v>985</v>
-      </c>
-      <c r="B3" s="67"/>
+      <c r="A3" s="111" t="s">
+        <v>969</v>
+      </c>
+      <c r="B3" s="112"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -11236,141 +11873,141 @@
       <c r="I3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="71" t="s">
-        <v>986</v>
-      </c>
-      <c r="B4" s="72"/>
+      <c r="A4" s="116" t="s">
+        <v>970</v>
+      </c>
+      <c r="B4" s="117"/>
       <c r="C4" s="4" t="s">
-        <v>987</v>
+        <v>971</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>989</v>
+        <v>973</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="71" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B5" s="72"/>
+      <c r="A5" s="116" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B5" s="117"/>
       <c r="C5" s="4" t="s">
-        <v>992</v>
+        <v>976</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>993</v>
+        <v>977</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>994</v>
+        <v>978</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="71" t="s">
-        <v>1064</v>
-      </c>
-      <c r="B6" s="72"/>
+      <c r="A6" s="116" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B6" s="117"/>
       <c r="C6" s="4" t="s">
-        <v>996</v>
+        <v>980</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>998</v>
+        <v>982</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B7" s="72"/>
+      <c r="A7" s="116" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B7" s="117"/>
       <c r="C7" s="4" t="s">
-        <v>1000</v>
+        <v>984</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>1001</v>
+        <v>985</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>1002</v>
+        <v>986</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="71" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B8" s="72"/>
+      <c r="A8" s="116" t="s">
+        <v>987</v>
+      </c>
+      <c r="B8" s="117"/>
       <c r="C8" s="4" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>1005</v>
+        <v>989</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>1006</v>
+        <v>990</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
-        <v>1080</v>
-      </c>
-      <c r="B9" s="72"/>
+      <c r="A9" s="116" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B9" s="117"/>
       <c r="C9" s="4" t="s">
-        <v>1008</v>
+        <v>992</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="71" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B10" s="72"/>
+      <c r="A10" s="116" t="s">
+        <v>995</v>
+      </c>
+      <c r="B10" s="117"/>
       <c r="C10" s="4" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>1128</v>
+        <v>1112</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>290</v>
@@ -11379,23 +12016,23 @@
         <v>307</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B11" s="72"/>
+      <c r="A11" s="116" t="s">
+        <v>999</v>
+      </c>
+      <c r="B11" s="117"/>
       <c r="C11" s="4" t="s">
-        <v>1016</v>
+        <v>1000</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>1129</v>
+        <v>1113</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>290</v>
@@ -11404,23 +12041,23 @@
         <v>307</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1018</v>
+        <v>1002</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="71" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B12" s="72"/>
+      <c r="A12" s="116" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B12" s="117"/>
       <c r="C12" s="4" t="s">
-        <v>1020</v>
+        <v>1004</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>1130</v>
+        <v>1114</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>290</v>
@@ -11429,23 +12066,23 @@
         <v>307</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>1022</v>
+        <v>1006</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B13" s="72"/>
+      <c r="A13" s="116" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B13" s="117"/>
       <c r="C13" s="4" t="s">
-        <v>1132</v>
+        <v>1116</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>1133</v>
+        <v>1117</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>290</v>
@@ -11454,256 +12091,256 @@
         <v>307</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>1134</v>
+        <v>1118</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="71" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B14" s="72"/>
+      <c r="A14" s="116" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B14" s="117"/>
       <c r="C14" s="4" t="s">
-        <v>1024</v>
+        <v>1008</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>1025</v>
+        <v>1009</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4" t="s">
-        <v>1026</v>
+        <v>1010</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B15" s="72"/>
+      <c r="A15" s="116" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B15" s="117"/>
       <c r="C15" s="4" t="s">
-        <v>1028</v>
+        <v>1012</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>1135</v>
+        <v>1119</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4" t="s">
-        <v>1030</v>
+        <v>1014</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="71" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B16" s="72"/>
+      <c r="A16" s="116" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B16" s="117"/>
       <c r="C16" s="4" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>1136</v>
+        <v>1120</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="73" t="s">
-        <v>1035</v>
-      </c>
-      <c r="B17" s="72"/>
+      <c r="A17" s="118" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B17" s="117"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4" t="s">
-        <v>1137</v>
+        <v>1121</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="71" t="s">
-        <v>1037</v>
-      </c>
-      <c r="B18" s="72"/>
+      <c r="A18" s="116" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B18" s="117"/>
       <c r="C18" s="4" t="s">
-        <v>1038</v>
+        <v>1022</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>1039</v>
+        <v>1023</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
         <v>111</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>1040</v>
+        <v>1024</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B19" s="72"/>
+      <c r="A19" s="116" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B19" s="117"/>
       <c r="C19" s="4" t="s">
-        <v>1042</v>
+        <v>1026</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>1139</v>
+        <v>1123</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>290</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>990</v>
+        <v>974</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="73" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B20" s="72"/>
+      <c r="A20" s="118" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B20" s="117"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>1140</v>
+        <v>1124</v>
       </c>
       <c r="I20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="74" t="s">
-        <v>1047</v>
-      </c>
-      <c r="B21" s="72"/>
+      <c r="A21" s="119" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B21" s="117"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>1048</v>
+        <v>1032</v>
       </c>
       <c r="I21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="71" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B22" s="67"/>
+      <c r="A22" s="116" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B22" s="112"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4" t="s">
-        <v>1050</v>
+        <v>1034</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>1051</v>
+        <v>1035</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B23" s="67"/>
+      <c r="A23" s="116" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B23" s="112"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4" t="s">
-        <v>1053</v>
+        <v>1037</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>1054</v>
+        <v>1038</v>
       </c>
       <c r="I23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="71" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B24" s="67"/>
+      <c r="A24" s="116" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B24" s="112"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4" t="s">
-        <v>1056</v>
+        <v>1040</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>1057</v>
+        <v>1041</v>
       </c>
       <c r="I24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B25" s="67"/>
+      <c r="A25" s="116" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B25" s="112"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4" t="s">
-        <v>1059</v>
+        <v>1043</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>1060</v>
+        <v>1044</v>
       </c>
       <c r="I25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="74" t="s">
-        <v>1061</v>
-      </c>
-      <c r="B26" s="75"/>
+      <c r="A26" s="119" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B26" s="120"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="s">
-        <v>1127</v>
+        <v>1111</v>
       </c>
       <c r="I26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="76"/>
+      <c r="A27" s="121"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
@@ -11712,12 +12349,12 @@
       <c r="H27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="86"/>
+      <c r="A28" s="131"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="86"/>
+      <c r="A29" s="131"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
     </row>
